--- a/avoti/Riga-SECAP-saturs.xlsx
+++ b/avoti/Riga-SECAP-saturs.xlsx
@@ -449,7 +449,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rīgas SECAP vidusposma pārskata vietnes saturs (darba versija)</t>
+          <t>Rīgas SECAP vidusposma pārskata vietnes saturs (gala versija, 2026. gada oktobris)</t>
         </is>
       </c>
     </row>
@@ -470,14 +470,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Teksti “Papildināt”, “Nepieciešama papildu informācija” un “…” vietnē tiek parādīti kā vieta, kur trūkst informācijas.</t>
+          <t>Saturs atbilst gala pārskatam (Riga-SECAP-vidusposma-parskats-2026). Ja pārskatā kaut kas tiek labots, izmaiņas jāieraksta arī šeit.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lapa Pasakumi: statuss – darba versija (REA vērtējums pēc pārskata teksta), jāpārbauda. Atļautās vērtības – lapā Statusi.</t>
+          <t>Lapa Pasakumi: statuss – REA vērtējums pēc pārskata teksta. Atļautās vērtības – lapā Statusi.</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Pārskatā nav pietiekamas informācijas – lūdzam papildināt.</t>
+          <t>Pārskata sagatavošanas laikā nebija pietiekamas informācijas par pasākuma īstenošanu.</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Pārskatā: “Plāna izstrāde vēl nav uzsākta.” (Pašvaldības ēku atjaunošanas plāns; daudzdzīvokļu ēku plāns – sk. Dz2.)</t>
+          <t>Plāna izstrāde vēl nav uzsākta (pašvaldības ēku atjaunošanas plāns; daudzdzīvokļu ēku plāns – sk. Dz2).</t>
         </is>
       </c>
       <c r="F5" s="3" t="n"/>
@@ -1001,7 +1001,7 @@
 Nepieciešama papildu informācija.</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
@@ -1120,7 +1120,7 @@
 Nepieciešama papildu informācija.</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
@@ -1173,7 +1173,7 @@
 Būvniecības jomā tiek īstenoti sadarbības projekti, izstrādē arī apkaimju resursu centru koncepts.</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>CURE+ | https://rea.riga.lv/projekti/cure/
@@ -1280,7 +1280,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Izvērtēti scenāriji, gatavots ESKO iepirkums; par citām darbībām nepieciešama informācija.</t>
+          <t>Izvērtēti scenāriji, gatavots ESKO iepirkums, luksoforu diodes nomainītas uz LED; par pārējām darbībām informācija tiks papildināta.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Plānā paredzēts 2022.–2023. gadā sagatavot investīciju plānu ielu apgaismojuma, elektrotīklu un balstu nomaiņai, izvērtējot arī iespēju slēgt ilgtermiņa energoefektivitātes pakalpojuma līgumu, jo 89 % ielu apgaismojuma veido nātrija spuldzes, kuru nomaiņa esošajā tempā aizņemtu vairākus gadus. Ielu apgaismojuma sadaļā plāns min arī vairākas papildu darbības – 45 dzīvsudraba gaismekļu nomaiņu, atlikušo luksoforu kvēlspuldžu nomaiņu uz LED, citu institūciju apsaimniekošanā esošo gaismekļu pārņemšanu un attālinātas viedās vadības sistēmas ieviešanu; informācija par to izpildi tiks papildināta.</t>
+          <t>Plānā paredzēts 2022.–2023. gadā sagatavot investīciju plānu ielu apgaismojuma, elektrotīklu un balstu nomaiņai, izvērtējot arī iespēju slēgt ilgtermiņa energoefektivitātes pakalpojuma līgumu, jo 89 % ielu apgaismojuma veido nātrija spuldzes, kuru nomaiņa esošajā tempā aizņemtu vairākus gadus. Ielu apgaismojuma sadaļā plāns min arī vairākas papildu darbības – 45 dzīvsudraba gaismekļu nomaiņu, atlikušo luksoforu kvēlspuldžu nomaiņu uz LED, citu institūciju apsaimniekošanā esošo gaismekļu pārņemšanu un attālinātas viedās vadības sistēmas ieviešanu. Luksoforu diožu nomaiņa uz LED ir veikta, bet informācija par pārējo darbību izpildi tiks papildināta.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Modernizācijas projekti saskaņā ar Investīciju plānu (skaits jāpapildina).</t>
+          <t>Investīciju plānā 2026.–2027. gadam – 29 apgaismojuma projekti, t. sk. 10 apgaismojuma izbūves projekti neapgaismotās vietās.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Saskaņā ar Investīciju plānā sniegto informāciju Rīgā tiek īstenoti … apgaismojuma modernizācijas projekti.</t>
+          <t>Saskaņā ar Investīciju plānā 2026.–2027. gadam sniegto informāciju Rīgā tiek īstenoti vai plānoti 29 ielu un pilsētvides apgaismojuma projekti (indikatīvi 75 milj. EUR): 10 apgaismojuma izbūves projekti līdz šim neapgaismotās vietās (4,2 milj. EUR) un 19 esošā apgaismojuma modernizācijas un atjaunošanas projekti (70,8 milj. EUR), t. sk. ielu apgaismes modernizācija un energoefektivitātes paaugstināšana visā pilsētā (60 milj. EUR). Četri projekti jau tiek īstenoti, pārējie ir apstiprināti plānā.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Pārskatā: “Pasākums netiek īstenots.”</t>
+          <t>Pasākums netiek īstenots.</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Pārskatā: “Pasākums daļēji īstenots.”</t>
+          <t>Pasākums daļēji īstenots.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
 Par ilgtermiņa vīziju var uzskatīt arī Rīgas Klimata līguma Rīcības plānu un Investīciju plānu, kas tika apstiprināti 2025. gadā. Lai gan šie dokumenti iezīmē mērķus, kas sasniedzami jau līdz 2030. gadam, izvērtējot šodienas situāciju, resursus un attīstības tendences, tie vērtējami kā pārāk ambiciozi – Rīgas kopējās emisijas (ieskaitot atkritumu sektoru), visticamāk, līdz 2030. gadam nesamazināsies par 53 % pret 2019. gadu. Lai gan Klimata līguma vīzija nav pilnā apjomā īstenojama šajā desmitgadē, plāns iezīmē nepieciešamos pasākumus galveno sektoru pārkārtošanai, pārstājot izmantot fosilos energoresursus.</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>ATELIER | https://rea.riga.lv/projekti/atelier/
@@ -2244,19 +2244,16 @@
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t>2025. gada beigās Rīgas CSS bija uzstādīti 2,6 GW siltumražošanas jaudas, no kurām lielāko daļu veido dabasgāzes ūdenssildāmie katli (1 564 MW) un koģenerācijas stacijas (212 MW), vienlaikus 45 % saražotās siltumenerģijas bija atjaunīgas izcelsmes. CSS attīstības stratēģijā ieteikts veikt padziļinātu esošo siltumavotu izvērtējumu un uzturēt pastāvīgu to efektivitātes rādītāju monitoringu (rīcībpolitika 02-2).
-AS “Rīgas siltums” SC “Imanta” nomainīts absorbcijas siltumsūknis dūmgāzu siltuma atgūšanai (aplēstais ietaupījums ~5 000 MWh dabasgāzes un ~1 000 tCO₂ gadā), un līdz 2027. gadam plānota biokurināmā katlumājas modernizācija ar absorbcijas siltumsūkņiem (~5 milj. EUR). Uzņēmuma energopārvaldības sistēma sertificēta atbilstoši ISO 50001 (2021, resertifikācija 2024).</t>
+AS “Rīgas siltums” SC “Imanta” nomainīts absorbcijas siltumsūknis dūmgāzu siltuma atgūšanai (aplēstais ietaupījums ~5 000 MWh dabasgāzes un ~1 000 tCO₂ gadā), un līdz 2027. gadam plānota biokurināmā katlumājas modernizācija ar absorbcijas siltumsūkņiem (~5 milj. EUR). Uzņēmuma energopārvaldības sistēma sertificēta atbilstoši ISO 50001 (2021, resertifikācija 2024).
+AS “Rīgas siltums” SC “Imanta” uzstādīts un ekspluatācijā nodots 49 MW elektrodu katls, kas ļauj efektīvāk izmantot elektroenerģiju periodos, kad tās cena ir zema, īpaši kombinācijā ar plānoto siltumenerģijas akumulācijas tvertni (sk. E5). Lai energoavotu efektivitāte turpinātu pieaugt, REA jāturpina sadarbība ar siltumenerģijas ražotājiem un jāpalielina izpētes un pilotprojektu skaits.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>3001, 3012</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+          <t>3001, 3013</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="n">
         <v>101</v>
       </c>
@@ -2309,12 +2306,12 @@
       <c r="H27" s="3" t="inlineStr">
         <is>
           <t>2025. gadā CSS turpgaitas temperatūra vidēji bija 69,5 °C, atgaitas – 43,4 °C. CSS attīstības stratēģijā ieteikts izpētīt teritorijas, kurās iespējams ieviest zemas temperatūras režīmu, un īstenot zemas temperatūras pilotprojektus (rīcībpolitika 03-1).
-AS “Rīgas siltums” turpina 4. paaudzes CSS projektus: zemas temperatūras grafiks ieviests, piem., A. Čaka ielā 123 un K. Barona ielā 112, uzsākts pieslēgums apbūves projektam Mežaparkā un Čiekurkalnā, un nākamajā periodā plānots pieslēgt RTU. 2024./2025. finanšu gadā izbūvēti, pārbūvēti vai atjaunoti 11,05 km siltumtīklu (aplēstais zudumu samazinājums 10 373 MWh un 1 224 tCO₂ gadā); 66 % uzņēmuma 768 km siltumtīklu ir pārbūvēti vai jaunizbūvēti. Zudumi apkures sezonā bija 9,7 %, gadā – 12,49 %. Tīklu modernizācijai noslēgts līgums ar Eiropas Padomes Attīstības banku par 40 milj. EUR investīciju portfeli.</t>
+AS “Rīgas siltums” turpina 4. paaudzes CSS projektus: zemas temperatūras grafiks ieviests, piem., A. Čaka ielā 123 un K. Barona ielā 112, uzsākts pieslēgums apbūves projektam Mežaparkā un Čiekurkalnā, un nākamajā periodā plānots pieslēgt RTU. 2024./2025. finanšu gadā izbūvēti, pārbūvēti vai atjaunoti 11,05 km siltumtīklu (aplēstais zudumu samazinājums 10 373 MWh un 1 224 tCO₂ gadā); 66 % uzņēmuma 768 km siltumtīklu ir pārbūvēti vai jaunizbūvēti. Zudumi aktīvajā apkures sezonā bija 9,77 %, gadā – 12,49 %. Tīklu modernizācijai noslēgts līgums ar Eiropas Padomes Attīstības banku par 40 milj. EUR investīciju portfeli.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3002, 3003</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2378,7 +2375,11 @@
 AS “Rīgas siltums” uzsācis siltumtīklu digitālā dvīņa pilotprojektu, centralizētas SCADA sistēmas ieviešanu, attālinātu skaitītāju nolasīšanu (NB-IoT, ~700 siltummezglu) un biokurināmā uzskaites digitalizāciju.</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
           <t>ENABLE DHC | https://rea.riga.lv/projekti/enable-dhc/</t>
@@ -2424,7 +2425,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Elektrodu katls SC “Imanta”, plānotas jaunas AER jaudas.</t>
+          <t>Elektrodu katls SC “Imanta”, biokurināmā katlu māja Rencēnu ielā, plānotas jaunas AER jaudas.</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
@@ -2436,20 +2437,18 @@
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Labā krasta apvienotajā zonā līdz 2028. gadam plānots ieviest 50 MW biomasas ūdenssildāmo katlu, 10 MW elektrodu katlu un 10 MW siltumsūkni, kas pēc stratēģijas aplēsēm samazinās CSS ražošanas emisijas no aptuveni 369 līdz 242 ktCO₂. Ambiciozais scenārijs līdz 2040. gadam paredz 396 MW jaunu AER jaudu, t. sk. 211 MW siltumsūkņu un elektrodu katlu.
+Lai veicinātu energoefektivitāti un vietējo AER izmantošanu centralizētajā siltumapgādē, 2023. gada nogalē tika īstenots projekts “Biokurināmā katlu mājas ar jaudu 48 MW izbūve Rencēnu ielā 30, Rīgā” ar 4 000 000 EUR Eiropas Kohēzijas fonda līdzfinansējumu.
 AS “Rīgas siltums” koncerns 2024./2025. finanšu gadā saražoja 48 % no Rīgas CSS nodotās siltumenerģijas – 70 % ar šķeldu (1 022 GWh), 30 % ar dabasgāzi; pārējo siltumenerģiju iepērk no neatkarīgajiem ražotājiem. SC “Imanta” 2025. gadā nodots ekspluatācijā 49 MW elektrodu katls (~20 GWh siltumenerģijas un ~4 000 tCO₂ ietaupījums gadā), un līdz 2028. gadam plānota 8 000 m³ (420 MWh) siltumakumulācijas tvertne. Uzņēmuma mērķis ir līdz 2030. gadam samazināt neto emisijas par 60 % pret 2019. gadu un sasniegt 70–80 % klimatneitrālas enerģijas īpatsvaru.
-AS “Rīgas siltums” uzstādījis trīs saules enerģijas stacijas ar kopējo jaudu 463,74 kW. AER risinājumus – saules paneļus un kolektorus – plānots ieviest mazas jaudas katlu mājās, kur tas ir tehniski un ekonomiski pamatoti.</t>
+AS “Rīgas siltums” uzstādījis trīs saules enerģijas stacijas ar kopējo jaudu 463,74 kW. AER risinājumus – saules paneļus un kolektorus – plānots ieviest mazas jaudas katlu mājās, kur tas ir tehniski un ekonomiski pamatoti.
+ES fondu projekts 4.3.1.0/22/A/001 “Biokurināmā katlu mājas ar jaudu 48 MW izbūve Rencēnu ielā 30, Rīgā”</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>3002, 3012</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+          <t>3002, 3013</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="n">
         <v>401883</v>
@@ -2502,7 +2501,7 @@
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Kā inovatīvi projekti izceļami AS “Rīgas siltums” SC “Imanta” uzstādītais 49 MW elektrodu katls, kā arī atlikumsiltuma izmantošanas izpēte un pilotēšana sadarbībā ar REA.
-Atlikumsiltums Rīgas CSS pagaidām praktiski netiek izmantots. Ambiciozajā scenārijā tā īpatsvars 2035. gadā sasniegtu 5,5 %, tuvojoties ES Elektrifikācijas rīcības plāna orientējošajam līmenim, ja attīstās datu centri un citi atlikumsiltuma avoti un tiek izveidots ekonomiski dzīvotspējīgs sadarbības modelis ar CSS. Izaugsmes un Ambiciozajā scenārijā paredzēta arī Daugavgrīvas notekūdeņu attīrīšanas iekārtu atlikumsiltuma (6 MW) integrācija.
+Atlikumsiltums no datu centriem un citiem ārējiem avotiem Rīgas CSS pagaidām praktiski netiek izmantots. Ambiciozajā scenārijā tā īpatsvars 2035. gadā sasniegtu 5,5 %, tuvojoties ES Elektrifikācijas rīcības plāna orientējošajam līmenim, ja attīstās datu centri un citi atlikumsiltuma avoti un tiek izveidots ekonomiski dzīvotspējīgs sadarbības modelis ar CSS. Izaugsmes un Ambiciozajā scenārijā paredzēta arī Daugavgrīvas notekūdeņu attīrīšanas iekārtu atlikumsiltuma (6 MW) integrācija.
 Projektā ENABLE DHC sadarbībā ar REA un SIA “Rīgas ūdens” veikta tehniski ekonomiskā izpēte siltuma atgūšanai no BAS “Daugavgrīva” un tā integrācijai Daugavgrīvas un Bolderājas CSS zonās; notiek scenāriju modelēšana. Kopā ar SIA “Tet” izvērtēti atlikumsiltuma un dzesēšanas risinājumi, un identificēts maza mēroga pilotprojekts.</t>
         </is>
       </c>
@@ -2561,10 +2560,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026. gada aprīlī CSS bija 8431 pieslēgums, un siltumtīklu kopgarums bija aptuveni 948 km. Jaunu tīklu izbūves temps pieaug – no 2,8 km 2022. gadā līdz 5,3 km 2025. gadā –, tomēr tīklu paplašināšanās (0,6 % gadā) ir krietni lēnāka par ES Elektrifikācijas rīcības plānā paredzēto (6–7 % gadā). CSS pieslēgti 58 % apsildāmās ēku platības, bet pēc stratēģijas aplēsēm CSS nodrošina ap 53 % no kopējā siltumenerģijas pieprasījuma (SECAP2030: 56 % 2020. gadā, mērķis – 60 %); atšķirība daļēji skaidrojama ar atšķirīgu aprēķina metodi. Kā perspektīvākās CSS attīstības teritorijas stratēģijā izceltas VEF, Skanste, Pārdaugava, Ķengarags un Bieriņi.
+          <t>Lai veicinātu jaunu klientu pieslēgšanu Rīgas pilsētas CSS ar mērķi uzlabot dabas aizsardzību un bioloģisko daudzveidību, “zaļo” infrastruktūru, it īpaši pilsētvidē, un samazināt piesārņojumu, AS “Rīgas siltums” iesaistījās projektā “Gaisa piesārņojuma samazināšanas pasākumi Rīgas valstspilsētas pašvaldībā”. Tas ļāva piesaistīt 2 535 430 EUR ERAF finansējuma siltumtīklu izbūvei, lai pieslēgtu objektus CSS.
+2026. gada aprīlī CSS bija 8431 pieslēgums, un siltumtīklu kopgarums bija aptuveni 948 km. Jaunu tīklu izbūves temps pieaug – no 2,8 km 2022. gadā līdz 5,3 km 2025. gadā –, tomēr tīklu paplašināšanās (0,6 % gadā) ir krietni lēnāka par ES Elektrifikācijas rīcības plānā paredzēto (6–7 % gadā). CSS pieslēgti 58 % apsildāmās ēku platības, bet pēc stratēģijas aplēsēm CSS nodrošina ap 53 % no kopējā siltumenerģijas pieprasījuma (SECAP2030: 56 % 2020. gadā, mērķis – 60 %); atšķirība daļēji skaidrojama ar atšķirīgu aprēķina metodi. Kā perspektīvākās CSS attīstības teritorijas stratēģijā izceltas VEF, Skanste, Pārdaugava, Ķengarags un Bieriņi.
 2024./2025. finanšu gadā CSS pieslēgtas 56 jaunas ēkas ar kopējo siltumslodzi 22,5 MW (44 labajā krastā, 12 kreisajā), un jaunu klientu pieslēgšanai izbūvēti 2,67 km siltumtīklu.
 Pieejams līdzfinansējums, tiek veikts komunikācijas darbs.
-Tiek uzturēts apkures katlu reģistrs.</t>
+Tiek uzturēts apkures katlu reģistrs.
+ES fondu projekts 2.2.3.5/1/24/I/002 “Gaisa piesārņojuma samazināšanas pasākumi Rīgas valstspilsētas pašvaldībā”</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2572,11 +2573,7 @@
           <t>3001</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
+      <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="n"/>
@@ -2629,14 +2626,10 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>3003, 3014, 3006, 3007</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
+          <t>3004, 3015, 3007, 3008</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
         <v>166486</v>
@@ -2700,7 +2693,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>3009, 3010, 3011, 1010</t>
+          <t>3010, 3011, 3012, 1010</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2835,12 +2828,8 @@
           <t>Nepieciešama papildu informācija</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="n">
         <v>185000</v>
       </c>
@@ -2963,6 +2952,8 @@
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t>2025. gadā “Rīgas satiksme” pārvadāja 118,5 milj. pasažieru (2023. gadā – 114,74 milj., 2024. gadā – 115,97 milj.). Pakalpojums tiek nodrošināts 79 tramvaju, trolejbusu un autobusu maršrutos ar kopējo maršrutu tīkla garumu 1 166,3 km; izpildīti 99,68 % reisu, un vidējais braukšanas ātrums pieaudzis līdz 20,03 km/h (2024. gadā – 19,53 km/h). Ar pakalpojuma pieejamību apmierināti 82 %, ar kvalitāti – 77 % klientu. 2025. gadā veiktas izmaiņas maršrutu tīklā, izveidoti jauni tramvaju savienojumi, un izmēģinājuma pievedošie maršruti pieņemti kā pastāvīgi. Nakts sabiedriskā transporta pilotprojektā pārvadāti 11 422 pasažieri. Metropoles mobilitātes integrācijai ieviesta Rīgas vienotā biļete ar “Pasažieru vilcienu” un noslēgts trīspusējs līgums starp Rīgas valstspilsētu, “Rīgas satiksmi” un Ropažu novadu – pirmais starppašvaldību sabiedriskā transporta līdzfinansēšanas modelis Latvijā. 2026. gada 1. jūnijā atklāts 7. tramvaja līnijas pagarinājums (2,2 km) līdz mobilitātes punktam “Ķengarags”, ko apkalpo 7. un 14. tramvajs, 15. trolejbuss un 49. autobuss. 2026. gadā plānots uzsākt priekšizpētes tramvaja līniju būvniecībai Skanstes un Ziepniekkalna apkaimēs.
+PAD maršrutu tīkla reformas pētījumā secināts, ka sistēmai ir plašs pārklājums (90 % iedzīvotāju dzīvo 400 m attālumā no pieturas) un augsta precizitāte (94 % reisu kavējas ne vairāk kā 5 minūtes), taču maršrutu tīkls nav būtiski pārskatīts vairāk nekā 30 gadus un ir izteikti orientēts uz centru: radiālie maršruti veido 58 % tīkla, vairāk nekā 55 % maršrutu maksimuma stundās kursē ar 20 minūšu vai lielāku intervālu, un darba braucienos starp apkaimēm ārpus centra sabiedriskā transporta īpatsvars bieži ir zem 10 %. Prioritātes pasākumu (sabiedriskā transporta joslas, prioritāte luksoforos) ir salīdzinoši maz. Pētījumā ieteikts veidot skaidrāku, hierarhisku tīklu ar spēcīgiem maģistrālajiem koridoriem, vienlaikus uzlabojot starpapkaimju savienojumus, un pilotēt ekspresreisus (piem., Brīvības ielas koridorā), jaunus starpapkaimju maršrutus un pieturu optimizāciju.
+Aptaujā 68 % iedzīvotāju pozitīvi vērtē sabiedriskā transporta atbilstību savām vajadzībām; svarīgākās ir precizitāte un regularitāte, un 58 % pasažieru piekristu braucieniem ar pārsēšanos, ja transports kursētu biežāk. Vienlaikus 6 % plāno sabiedrisko transportu izmantot biežāk, bet 13 % – retāk vai to pārtraukt, galvenokārt, lai vairāk brauktu ar automašīnu.
 Atveseļošanas fonda transporta zaļināšanas reformā plānotā metrobusa līnija Dzelzavas ielā 2024. gadā netika īstenota, un tās finansējums novirzīts Rail Baltica projektam.</t>
         </is>
       </c>
@@ -2971,11 +2962,7 @@
           <t>4005, 4006</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="n">
         <v>185700</v>
       </c>
@@ -3032,7 +3019,8 @@
       <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Zemo emisiju zonas projekta (PAD pārziņā) tālāka virzība kopš 2026. gada pavasara ir apturēta. Zona bija viena no REA vadītā NetZeroCities pilotprojekta SEED galvenajām tēmām – sadarbībā ar partneriem īstenoti gaisa kvalitātes mērījumi, iesaistot skolēnus, un mobilitātes paradumi apspriesti fokusgrupās un aptaujās; rezultāti noderēja arī zonas projekta vadītājiem. Jāņem vērā, ka zemo emisiju zonas primārais mērķis ir gaisa kvalitātes uzlabošana, un tai nav viennozīmīgi lielākā ietekme uz pilsētas SEG emisijām.
-2026. gada augustā rosināts izveidot Rīgas autonovietņu un mobilitātes attīstības komisiju, kuras pirmais uzdevums būtu stāvparku plānošana pie pilsētas robežas un lielākajiem transporta mezgliem. Tiek apspriestas arī izmaiņas stāvvietu regulējumā, t. sk. elektroauto bezmaksas stāvēšanas priekšrocību pakāpeniska ierobežošana no 2027. gada.</t>
+2026. gada augustā rosināts izveidot Rīgas autonovietņu un mobilitātes attīstības komisiju, kuras pirmais uzdevums būtu stāvparku plānošana pie pilsētas robežas un lielākajiem transporta mezgliem. Tiek apspriestas arī izmaiņas stāvvietu regulējumā, t. sk. elektroauto bezmaksas stāvēšanas priekšrocību pakāpeniska ierobežošana no 2027. gada.
+Maršrutu tīkla reformas pētījumā secināts, ka piekļuve centram ar automašīnu joprojām ir ērta – stāvvietu piedāvājums ir plašs, maksa tiek uztverta kā zema, un Rīgā nav izveidota stāvparku (P&amp;R) sistēma. Biežākais iemesls sabiedriskā transporta izmantošanai aptaujā (46 %) ir tas, ka nav jāmeklē un jāapmaksā stāvvieta. Līdz 2030. gadam ieteikts pilotēt stāvparkus pie galvenajiem iebraukšanas ceļiem ar biežu sabiedrisko transportu (piem., Juglā), pakāpeniski samazināt stāvvietu skaitu un pārskatīt cenas centrā, kā arī jaunās attīstības teritorijās ar labu sabiedriskā transporta pieejamību noteikt zemākus maksimālos stāvvietu normatīvus.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -3100,7 +3088,8 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Rīgā izveidots 15 mobilitātes punktu tīkls pie dzelzceļa stacijām un pieturām (ES kohēzijas politikas 2021–2027 pasākums 2.3.1.2 “Multimodāls sabiedriskā transporta tīkls”). 2026. gada septembrī Rīgas dome atbalstīja vēl desmit mobilitātes punktu izveidi līdz 2029. gada beigām (līdz 26,6 milj. EUR, t. sk. 15 milj. EUR ERAF), tostarp pie Centrālās stacijas un Starptautiskās autoostas. https://www.riga.lv/lv/mobilitates-punktu-buvnieciba</t>
+          <t>Rīgā izveidots 15 mobilitātes punktu tīkls pie dzelzceļa stacijām un pieturām (ES kohēzijas politikas 2021–2027 pasākums 2.3.1.2 “Multimodāls sabiedriskā transporta tīkls”). 2026. gada septembrī Rīgas dome atbalstīja vēl desmit mobilitātes punktu izveidi līdz 2029. gada beigām (līdz 26,6 milj. EUR, t. sk. 15 milj. EUR ERAF), tostarp pie Centrālās stacijas un Starptautiskās autoostas. https://www.riga.lv/lv/mobilitates-punktu-buvnieciba
+Maršrutu tīkla reformas pētījuma dati liecina, ka koplietošanas mobilitāte pašlaik konsekventi nedarbojas kā pirmā/pēdējā kilometra risinājums sabiedriskajam transportam: koplietošanas automašīnas bieži aizstāj braucienus uz teritorijām ārpus sabiedriskā transporta pārklājuma, bet mikromobilitātes braucieni koncentrējas centrā. Pētījumā ieteikts pilnveidot mobilitātes punktus un savienojumus ar dzelzceļu – aptaujā biežāku sabiedriskā transporta lietošanu plāno tieši vilciena un mikromobilitātes lietotāji.</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -3108,11 +3097,7 @@
           <t>4001, 4008</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="n">
         <v>131500</v>
       </c>
@@ -3177,11 +3162,7 @@
           <t>4002, 4003</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="n">
         <v>74000</v>
       </c>
@@ -3243,11 +3224,7 @@
           <t>1014, 1015</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="n"/>
       <c r="L41" s="3" t="n"/>
       <c r="M41" s="3" t="n"/>
@@ -3298,7 +3275,7 @@
           <t>PAD piedalās Horizon Europe projektā UNCHAIN (2023–2026), kurā analizētas pilsētas kravu pārvadājumu datu plūsmas un izstrādātas vadlīnijas pilsētas loģistikas platformai, t. sk. iekraušanas un izkraušanas plānošanai vēsturiskajā centrā. Zemo emisiju zonas projektā iegādāti 2022. gada kravu transporta kustības dati.</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t>UNCHAIN (Horizon Europe) | https://www.rdpad.lv/portfolio/kravu-parvadajumu-pieprasijuma-prognozesana-un-digitalizacija-pilsetas-logistikas-planosanas-veicinasanai-unchain/</t>
@@ -3360,11 +3337,7 @@
           <t>4007, 4009</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="n">
         <v>63500</v>
       </c>
@@ -3407,7 +3380,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Aprakstītas AS “Sadales tīkls” investīcijas; pašvaldības izvērtējums nav minēts – jāprecizē.</t>
+          <t>Aprakstītas AS “Sadales tīkls” investīcijas; pašvaldības izvērtējums pārskatā nav aprakstīts.</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -3430,11 +3403,7 @@
           <t>4002, 4003</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
@@ -3486,12 +3455,8 @@
 https://www.riga.lv/lv/jaunums/riga-saks-istenot-pilotprojektu-pasazieru-kugu-satiksmei-starp-bolderaju-un-vecmilgravi</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="n"/>
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n"/>
@@ -3538,10 +3503,11 @@
       <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Mobilitātes paradumi tiek apzināti aptaujās. NetZeroCities pilotprojektā SEED un iniciatīvā “Elpo Rīga”, kas noslēdzās 2026. gada aprīlī, veikts pētījums par mobilitātes paradumiem; iedzīvotāju mobilitātes aptaujas veic arī CSP.
-Rīgas plānošanas reģions Interreg Centrālbaltijas projektā SuRuMo, izmantojot mobilo operatoru datus, izstrādā rīku iedzīvotāju pārvietošanās paradumu kartēšanai, ko plānots ieviest 2026. gada beigās.</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr"/>
+Rīgas plānošanas reģions Interreg Centrālbaltijas projektā SuRuMo, izmantojot mobilo operatoru datus, izstrādā rīku iedzīvotāju pārvietošanās paradumu kartēšanai, ko plānots ieviest 2026. gada beigās.
+2025. gada septembrī PAD sabiedriskā transporta maršrutu tīkla reformas pētījumā veikta iedzīvotāju aptauja (Kantar, n = 2500, Rīga un pierobežas pašvaldības), un pētījumā analizēti arī e-talonu validāciju un GTFS dati. Aptauja raksturo pārvietošanās veidu izmantošanas biežumu, bet ne braucienu sadalījumu, tāpēc privāto automašīnu lietotāju īpatsvara mērķa monitoringam joprojām nepieciešama regulāra, braucienos balstīta mobilitātes aptauja.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
           <t>NetZeroCities SEED / Elpo Rīga pārskats | https://rea.riga.lv/wp-content/uploads/2026/04/Elpo-Riga-parskats_garais_20_04_2026.pdf
@@ -3585,7 +3551,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Dati tiek uzkrāti LVC un ĀMD sistēmās; viedā skaitīšanas sistēma nav minēta.</t>
+          <t>Dati tiek uzkrāti LVC un ĀMD sistēmās; viedās skaitīšanas sistēma pārskatā nav aprakstīta.</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -3608,11 +3574,7 @@
           <t>4001</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="n"/>
       <c r="L47" s="3" t="n"/>
       <c r="M47" s="3" t="n"/>
@@ -3661,12 +3623,8 @@
           <t>Rīgas digitālā aģentūra izstrādā Rīgas transporta modeli vienotas mobilitātes datu ekosistēmas projektā (https://www.riga.lv/lv/projekts/vienotas-mobilitates-datu-ekosistemas-izveide). REA eksperti aicinājuši tajā iestrādāt SEG emisiju aprēķina funkcionalitāti.</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="n"/>
       <c r="L48" s="3" t="n"/>
       <c r="M48" s="3" t="n"/>
@@ -3751,7 +3709,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Energopārvaldības sistēma darbojas un ir sertificēta (424 objekti), enerģijas patēriņš pašvaldības ēkās samazinājies par 13,7 %, un ielu apgaismojuma īpatnējais patēriņš samazinājies līdz 0,392 MWh uz gaismekli – šie mērķi ir sasniegti vai atbilst trajektorijai. Atpaliek AER īpatsvara palielināšana siltumapgādē, elektroapgādē un pašvaldības autoparkā (elektroauto – 12,0 %), un pašvaldības infrastruktūras emisijas samazinājušās par 27,3 % (mērķis −100 %).</t>
+          <t>Energopārvaldības sistēma darbojas un ir sertificēta (424 objekti), enerģijas patēriņš pašvaldības ēkās samazinājies par 13,7 %, ielu apgaismojuma īpatnējais patēriņš samazinājies līdz 0,392 MWh uz gaismekli, un luksoforos veikta diožu nomaiņa uz LED – šie mērķi ir sasniegti vai atbilst trajektorijai. Atpaliek AER īpatsvara palielināšana siltumapgādē, elektroapgādē un pašvaldības autoparkā (elektroauto – 12,0 %), un pašvaldības infrastruktūras emisijas samazinājušās par 27,3 % (mērķis −100 %).</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -3778,7 +3736,7 @@
 Ūdenssaimniecības elektroenerģijas patēriņa emisijas (rādītājs 1019) kopš 2020. gada praktiski nav mainījušās. SIA “Rīgas ūdens” dekarbonizācijas ceļa karte paredz līdz 2040. gadam samazināt 1. un 2. tvēruma SEG emisijas par 54 % (pret 2020.–2023. gada vidējo līmeni – 9 249 tCO₂e) un panākt notekūdeņu attīrīšanas energoneitralitāti, galvenokārt paplašinot biogāzes ražošanu, uzstādot saules elektrostacijas un uzlabojot energoefektivitāti; uzņēmums ir sertificējis energopārvaldības sistēmu atbilstoši ISO 50001.</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3796,7 +3754,7 @@
           <t>Siltumenerģijas patēriņš CSS pieslēgtajās ēkās ar klimata korekciju samazinājies par 8,6 % un atbilst trajektorijai, taču atjaunotas tikai 209 ēkas no 2000 – REA vērtējumā šis mērķis līdz 2030. gadam nav sasniedzams.</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Ēku atjaunošana daudzdzīvokļu ēku sektorā virzās lēni, tāpēc tās ietekme uz Rīgas CO₂ emisiju samazinājumu joprojām ir neliela.
@@ -3837,23 +3795,23 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>AER īpatsvars Rīgas pilsētas CSS pieaudzis līdz 46,85 %, dabasgāzes patēriņš samazinājies par 27,3 %, un decentralizētās siltumapgādes īpatsvars – līdz 42,7 %. Tomēr AER īpatsvars decentralizētajā siltumapgādē samazinājies (34,2 %), AER īpatsvars Rīgā saražotajā elektroenerģijā ir tikai 6,7 %, un enerģijas ražošanas emisijas samazinājušās par 12,6 % pret 2019. gadu (mērķis −30 %).</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
+          <t>AER īpatsvars Rīgas pilsētas CSS pieaudzis līdz 45,5 %, dabasgāzes patēriņš samazinājies par 27,3 %, un decentralizētās siltumapgādes īpatsvars – līdz 42,7 %. Tomēr AER īpatsvars decentralizētajā siltumapgādē samazinājies (34,2 %), AER īpatsvars Rīgā saražotajā elektroenerģijā ir tikai 6,7 %, un enerģijas ražošanas emisijas samazinājušās par 12,6 % pret 2019. gadu (mērķis −30 %).</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AER īpatsvars Rīgas pilsētas CSS pieaudzis no 31 % 2020. gadā līdz 47 % 2025. gadā, un šis mērķis atbilst trajektorijai, lai līdz 2030. gadam AER pārsniegtu 66 %.
-Problemātiskākais aspekts ir augstais decentralizētās siltumapgādes īpatsvars (dabasgāzes katli, ietekme uz gaisa kvalitāti). Pēc SEG inventarizācijas datiem tas 2025. gadā bija 42,7 % (2020. gadā – 49,9 %), un šis mērķis atbilst trajektorijai. Savukārt AER īpatsvars decentralizētajā siltumapgādē samazinājies no 41,8 % 2020. gadā līdz 34,2 % 2025. gadā – progresa nav, un gada vērtības svārstās (34–43 %), jo mainās biomasas sadalījums starp CSS un decentralizēto apgādi. Abu mērķu bāzes vērtības atšķiras no SECAP2030 (44 % un 42 %, 2019), jo tās nevar atkārtot ar inventarizācijas datiem, tāpēc progress mērīts pret 2020. gadu.
-Decentralizētās siltumapgādes īpatsvaru būtiski ietekmē aprēķina metode. SEG inventarizācijā to nosaka pēc patērētā kurināmā (42,7 % 2025. gadā), savukārt CSS attīstības stratēģijas 2. redakcijā tas aplēsts pēc apsildāmās ēku platības un īpatnējā patēriņa – aptuveni 47 % no kopējā siltumenerģijas pieprasījuma (5,4 TWh). Pēc stratēģijas aplēsēm 40 % mērķis līdz 2030. gadam ir maz ticams un pat Ambiciozajā scenārijā tiktu sasniegts tikai ap 2040. gadu. Tādēļ šī mērķa statuss vērtējams piesardzīgi, un SECAP2030 aktualizācijā jāvienojas par vienotu aprēķina metodi. Savukārt AER īpatsvars CSS visos stratēģijas scenārijos 2030. gadā sasniedz 72–82 %, tātad SECAP2030 mērķis (≥ 66 %) ir sasniedzams.
-Stratēģijā siltumtīklu zudumi 2025. gadā aplēsti 12 % apmērā gadā un 9,8 % apkures sezonā; apkures sezonas rādītājs jau atbilst NEKP mērķim (&lt; 10 %) un varētu aizstāt pašreizējo mērķi SECAP2030 aktualizācijā.
+          <t>AER īpatsvars Rīgas pilsētas CSS pieaudzis no 31,5 % 2020. gadā līdz 45,5 % 2025. gadā. Progress līdz 2030. gada mērķim (≥ 66 %) ir 41 %, tāpēc šis mērķis nedaudz atpaliek no trajektorijas.
+Problemātiskākais aspekts ir augstais decentralizētās siltumapgādes īpatsvars (dabasgāzes katli, ietekme uz gaisa kvalitāti). Pēc SEG inventarizācijas datiem tas 2025. gadā bija 42,7 % (2020. gadā – 49,9 %), un šis mērķis atbilst trajektorijai. Savukārt AER īpatsvars decentralizētajā siltumapgādē samazinājies no 41,8 % 2020. gadā līdz 34,2 % 2025. gadā – mērķis atpaliek no trajektorijas un progresa nav, taču gada vērtības svārstās (34–43 %), jo mainās biomasas sadalījums starp CSS un decentralizēto apgādi. Abu mērķu bāzes vērtības atšķiras no SECAP2030 (44 % un 42 %, 2019), jo tās nevar atkārtot ar inventarizācijas datiem, tāpēc progress mērīts pret 2020. gadu.
+Decentralizētās siltumapgādes īpatsvaru būtiski ietekmē aprēķina metode. SEG inventarizācijā to nosaka pēc patērētā kurināmā (42,7 % 2025. gadā), savukārt CSS attīstības stratēģijas 2. redakcijā tas aplēsts pēc apsildāmās ēku platības un īpatnējā patēriņa – aptuveni 47 % no kopējā siltumenerģijas pieprasījuma (5,4 TWh). Pārrēķinot decentralizēto kurināmā patēriņu siltumenerģijā (pieņemot 92 % lietderību), īpatsvars būtu aptuveni 41 %, tātad atkarībā no metodes 2025. gada vērtība ir robežās no 41 % līdz 47 %. Pēc stratēģijas aplēsēm 40 % mērķis līdz 2030. gadam ir maz ticams un pat Ambiciozajā scenārijā tiktu sasniegts tikai ap 2040. gadu. Tādēļ šī mērķa statuss vērtējams piesardzīgi, un SECAP2030 aktualizācijā jāvienojas par vienotu aprēķina metodi. Savukārt AER īpatsvars CSS visos stratēģijas scenārijos 2030. gadā sasniedz 72–82 %, tātad SECAP2030 mērķis (≥ 66 %) ir sasniedzams.
+Siltumenerģijas zudumu mērķis vidusposmā mainīts atbilstoši NEKP2030 pasākuma 3.1.3.11 rezultatīvajam rādītājam (siltuma zudumu īpatsvars apkures sezonā &lt; 10 % līdz 2030. gadam): SECAP2030 mērķa (relatīvie gada zudumi 11,6 %) vietā tiek vērtēti zudumi siltumtīklos aktīvajā apkures sezonā (oktobris–aprīlis). Tāda pati norma iekļauta CSS attīstības stratēģijas 2026.–2040. gadam konceptuālajā ziņojumā. 2024./2025. finanšu gadā zudumi apkures sezonā bija 9,77 %, tātad mērķis ir sasniegts; gada zudumi bija 12,49 %. Zudumus būtiski ietekmē laikapstākļi (āra temperatūra, apkures sezonas ilgums), tāpēc gadu vērtības nav tieši salīdzināmas. 2025./2026. finanšu gadā zudumi apkures sezonā bija 9,30 %, gadā – 11,8 %.
 AER īpatsvars Rīgā saražotajā elektroenerģijā 2025. gadā bija 6,7 %. To galvenokārt nosaka dabasgāzes TEC atrašanās Rīgā, tāpēc ar lokāliem risinājumiem ēkās kopējo rādītāju nav iespējams būtiski palielināt.
 Kopumā Rīgas CO₂ emisijas enerģijas ražošanā būtiski ietekmē nacionāla mēroga infrastruktūra, tāpēc dekarbonizācijas pasākumus ne vienmēr ir iespējams īstenot pašvaldības ietvaros.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Patērētājiem piegādātā siltuma apjoms pārskata periodā nav būtiski mainījies. Savukārt AER īpatsvars pieaudzis salīdzinoši strauji – kopš 2020. gada par gandrīz 16 procentpunktiem.
+          <t>Patērētājiem piegādātā siltuma apjoms pārskata periodā nav būtiski mainījies. Savukārt AER īpatsvars pieaudzis salīdzinoši strauji – kopš 2020. gada par 14 procentpunktiem.
 Dabasgāzes patēriņa izmaiņas atšķiras mājokļu un pārējo lietotāju sektoros. Lielāko īpatsvaru veido sabiedriskais sektors un pārējie lietotāji, kur patēriņš kopš 2020. gada sarucis par trešdaļu jeb 33,7 %. Mājokļu sektorā patēriņš ir maz mainījies pēdējo četru gadu laikā, nedaudz samazinoties. 2020. un 2021. gada rādītāji ir izteikti atšķirīgi.
 Sadalītās elektroenerģijas apjoms Rīgā kopš 2020. gada ir palielinājies par 0,5 %. Tā kā elektrifikācija transporta un siltumapgādes jomās ir vēlama, pieaugums nav vērtējams negatīvi.
 Juridisko personu tīklā nodotās saules elektroenerģijas apjoms Rīgā kopš 2020. gada pieaudzis vairāk nekā simtkārtīgi – līdz 70,6 GWh 2025. gadā. Neraugoties uz transporta un apkures elektrifikācijas pieaugumu, elektroenerģijas tīkla jaudas Rīgā ir pieejamas – iedzīvotāji arvien biežāk nomaina malkas, gāzes u. c. apkures sistēmas pret siltumsūkņiem vai citiem elektroenerģijā balstītiem risinājumiem.
@@ -3885,10 +3843,11 @@
           <t>AER īpatsvars sabiedriskajā transportā sasniedzis 35,4 % un atbilst trajektorijai, bet transporta emisijas samazinājušās tikai par 6,2 % pret 2019. gadu un par 26,3 % pārsniedz 1990. gada līmeni (pieļaujams +21,5 %). Lielākā daļa transporta emisiju (720 no 758 ktCO₂) rodas privātajā transportā.</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Transporta jomas politikas plānošana, pasākumu ieviešana un monitorings ir Pilsētas attīstības departamenta (PAD), Ārtelpas un mobilitātes departamenta (ĀMD) un SIA “Rīgas satiksme” kompetencē, bet REA veic ikgadējo transporta emisiju monitoringu. Emisijas tiek aprēķinātas, balstoties uz aplēsēm par patērētās degvielas apjomu, tāpēc, piemēram, veloinfrastruktūras attīstības ietekme aprēķinā tiešā veidā neparādās. Privāto automašīnu lietotāju īpatsvara novērtēšanai būtu nepieciešami mobilitātes aptauju dati.
+          <t>Transporta jomas politikas plānošana, pasākumu ieviešana un monitorings ir Pilsētas attīstības departamenta (PAD), Ārtelpas un mobilitātes departamenta (ĀMD) un SIA “Rīgas satiksme” kompetencē, bet REA veic ikgadējo transporta emisiju monitoringu. Emisijas tiek aprēķinātas, balstoties uz aplēsēm par patērētās degvielas apjomu, tāpēc, piemēram, veloinfrastruktūras attīstības ietekme aprēķinā tiešā veidā neparādās.
+Privāto automašīnu lietotāju īpatsvara mērķa (37,4 % 2030. gadā; bāze – 42,4 % braucienu 2019. gadā pēc SUMBA mājsaimniecību aptaujas) izpildi vidusposmā nevar novērtēt, jo nav salīdzināmu braucienu datu. Indikatīvu priekšstatu sniedz PAD maršrutu tīkla reformas pētījumā 2025. gada septembrī veiktā iedzīvotāju aptauja (n = 2500, 16–75 g. v.): 48 % Rīgas iedzīvotāju regulāri (2–3 reizes nedēļā vai biežāk) pārvietojas pa Rīgu ar privāto automašīnu (paši pie stūres), bet 51 % regulāri izmanto sabiedrisko transportu; 34 % regulāri brauc tikai ar automašīnu, 37 % – tikai ar sabiedrisko transportu. Pierīgas iedzīvotāju vidū, kas regulāri uzturas Rīgā, regulāro autobraucēju ir 68 %. Aptauja mēra pārvietošanās veidu izmantošanas biežumu, nevis braucienu sadalījumu, tāpēc tās rezultāti nav tieši salīdzināmi ar SECAP2030 bāzes vērtību. Salīdzināmus datus varētu sniegt RMA SUMP vajadzībām 2026. gadā veiktā mobilitātes aptauja (sk. T1).
 Saskaņā ar “Rīgas satiksmes” ilgtspējas pārskatu 2025. gadā uzņēmuma kopējās SEG emisijas bija 63 923 tCO₂e (2024. gadā – 66 597 tCO₂e, 2023. gadā – 67 268 tCO₂e), t. i., par aptuveni 5 % mazāk nekā 2023. gadā, galvenokārt autoparka elektrifikācijas un energoefektivitātes uzlabojumu dēļ. Dīzeļdegviela veidoja 86,6 % no 1. līmeņa un 46,1 % no visām uzņēmuma SEG emisijām. Bezemisiju transportlīdzekļi (tramvaji, trolejbusi un elektroautobusi) veido 51 % no pārvadājumos iesaistītā autoparka, un vairāk nekā 90 % no uzņēmuma patērētās elektroenerģijas tiek izmantoti elektrotransporta kustības nodrošināšanai. Uzņēmuma saules paneļi (150 kW, 6. autobusu parks Kleistu ielā 28) 2025. gadā saražoja 136,6 MWh jeb aptuveni 0,25 % no uzņēmuma elektroenerģijas patēriņa; 2026. gadā plānots nodot ekspluatācijā vēl divas 75 kW saules elektrostacijas (Vestienas ielā 35 un Brīvības ielā 191). AER īpatsvars sabiedriskajā transportā pārskatā kā atsevišķs rādītājs nav norādīts.</t>
         </is>
       </c>
@@ -3916,7 +3875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3948,1574 +3907,1524 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Liels pašvaldības ēku skaits un daudzas iesaistītās puses</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Nav izmaiņu.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Trūkst ticamu datu par pašvaldības ēku apkurināmajām platībām, to tehnisko stāvokli, noslogojumu</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Precizētas ēku platības un kadastra numuri, 313 ēkām izstrādāti energosertifikāti.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Caurspīdīgu un ticamu datu trūkums par patēriņiem un to rādītājiem pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Uzlabota datu apmaiņa; patēriņš tiek uzskaitīts reizi mēnesī, tiek izstrādāta ikstundas datu platforma.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Sertificētas energopārvaldības sistēmas neesamība un neatbilstība normatīvajiem aktiem</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>EPS darbojas un tiek pilnveidota.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Pārskatāmu rīcību plānošana un īstenošana</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Panākts progress, jāstiprina sadarbība starp REA un Īpašuma departamentu (ĪD).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Augsti īpatnējie enerģijas patēriņi atjaunotajās ēkās</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Nepieciešama papildu informācija.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Augsts fosilā kurināmā īpatsvars pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Dabasgāzes katlu nomaiņa notiek lēni, taču kopējais patēriņš samazinājies par 12,4 %. Individuālo apkures katlu (granulas, dīzeļdegviela, sašķidrinātā gāze) patēriņa uzskaite vēl nav ieviesta.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Pašvaldības ēkās</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Gaisa kvalitāte un ventilācija izglītības iestādēs</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Nepieciešama papildu informācija.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Ielu apgaismojuma sektorā</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Plaša ielu apgaismojuma sistēma</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Nav izmaiņu.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Ielu apgaismojuma sektorā</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Stratēģijas iztrūkums</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Izvērtēti dažādi scenāriji, tiek gatavots iepirkums energoefektivitātes pakalpojuma (ESKO) līguma slēgšanai.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Ielu apgaismojuma sektorā</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Energopārvaldības sistēmas, t.sk. enerģijas monitoringa, iztrūkums</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Sistēma ieviesta.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Ielu apgaismojuma sektorā</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Augsts īpatnējais elektroenerģijas patēriņš uz gaismekli</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Patēriņš samazinās, pieaugot LED īpatsvaram.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Ielu apgaismojuma sektorā</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Novecojuši balsti</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Nepieciešama papildu informācija.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Ielu apgaismojuma sektorā</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Apgaismojuma nodrošināšana neapgaismotajās vietās, īpaši pilsētas nomalēs</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Modernizācijas projekti tiek īstenoti saskaņā ar Investīciju plānu.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Ielu apgaismojuma sektorā</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Atjaunīgās elektroenerģijas izmantošana ielu apgaismojuma nodrošināšanā</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Pašvaldībā ir vienots elektroenerģijas iepirkums, tāpēc atsevišķa atjaunīgās elektroenerģijas iegāde ielu apgaismojumam netiek īstenota.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Ielu apgaismojuma sektorā</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Augsts elektroenerģijas patēriņš luksoforiem</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Veikta luksoforu diožu nomaiņa uz LED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>pas</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pašvaldības transporta sektors</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apzinātu pašvaldības iestāžu autoparku, sistemātiski apkopotu datu par degvielas patēriņu, transportlīdzekļu nobraukumu trūkums; sistēmas datu regulārai atjaunošanai un analīzei trūkums</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Uzskaiti veic Finanšu departaments. Nav ieviesta vienota sistēma autoparka izmantošanas plānošanai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>pas</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pašvaldības transporta sektors</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Finansējuma pieejamība alternatīvās degvielas transportlīdzekļu (īpaši bezemisiju) skaita būtiskai palielināšanai pašvaldības autoparkā</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Elektroauto skaits ir pieaudzis gan administrācijas, gan kapitālsabiedrību autoparkā. Tomēr nav vienota risinājuma visa autoparka nomaiņai, ieskaitot lielākas noslodzes transportlīdzekļus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pas</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pašvaldības transporta sektors</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vāja transportlīdzekļu izmantošanas efektivitāte (neefektīvs nobraukums)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nav vienotas uzskaites pašvaldības mērogā, bet iespējama atšķirīga situācija dažādu organizāciju ietvaros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Izejas datu pieejamība un ticamība daudzdzīvokļu ēku energoefektivitātes līmeņa izvērtējumam.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ierobežojumi joprojām pastāv, tomēr pārskata periodā sasniegts būtisks progress energoefektivitātes datu jomā – ĢeoRīga tematiskās kartes, energosertifikāti, datu publicēšana un apmaiņa ar citām institūcijām.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lielākais siltumenerģijas patēriņš un CO₂ emisiju avots Rīgas pilsētas CSS.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nav notikušas būtiskas pārmaiņas. Aktīvāku lomu uzņemas siltumapgādes sistēmas operators un māju apsaimniekošanas uzņēmumi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Dzīvojamās ēkas ir gan fiziski, gan morāli novecojušas, un revitalizācijas pasākumi netiek veikti pietiekamā apjomā.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Izaicinājums nav mazinājies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Zems atjaunoto daudzdzīvokļu ēku īpatsvars (1,4 % jeb 159 ēkas). Iedzīvotāju zemā interese par daudzdzīvokļu ēku atjaunošanu.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Atjaunoto ēku kopskaits joprojām ir mazs (209 ēkas 2025. gadā), taču iedzīvotāju interese ir pieaugusi – dominē finanšu un administratīvie šķēršļi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Nav izstrādāta daudzdzīvokļu ēku atjaunošanas stratēģija, pašvaldības līmenī nav noteikta atbildīgā iestāde, kura sistemātiski risinātu šos jautājumus.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026. gadā notiek Ēku atjaunošanas plāna izstrāde, kas ir priekšnoteikums arī pašvaldības līmeņa stratēģijas definēšanai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pašvaldības namu apsaimniekotāja sliktā reputācija ēku atjaunošanas projektu organizēšanā.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Rīgas namu pārvaldnieka darbā panākti uzlabojumi. Ar Privatizācijas pabeigšanas likumu (spēkā no 2025. gada 1. maija) māju īpašniekiem jāpārņem pārvaldīšanas tiesības, un pašvaldība nolēmusi izbeigt līdzdalību uzņēmumā.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Daudzdzīvokļu ēku ar nelielu dzīvokļu skaitu atjaunošana, kas ir tehniski sliktā stāvoklī jeb ekspluatācijai bīstamās ēkas. Piem., divstāvu koka apbūves ēkas Maskavas forštatē, Vecmīlgrāvī, Sarkandaugavā, Vecpilsētā un Centra rajonā.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Atsevišķi labi piemēri, bet vispārēja risinājuma nav.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Daudzdzīvokļu ēku atjaunošana, kas atbilst kultūras pieminekļu statusam.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Atsevišķi labi piemēri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Daudzdzīvokļu ēku īpašnieku biedrību loma ēku atjaunošanā ir būtiska. Zema iedzīvotāju aktivitāte, kas ierobežo biedrību dibināšanu. Nav zināms kopējais biedrību skaits un sarežģīta to identificēšana.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ir mainīts normatīvais regulējums, paredzot alternatīvu biedrību dibināšanai – lēmumu pieņemšanu dzīvokļu īpašnieku kopībā.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Individuālās siltumenerģijas uzskaites sistēmas izveide līdz 2027. gadam.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ieviešanas progress atšķiras atkarībā no ēkas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Netiek pietiekami aktīvi izmantots pieejamais līdzfinansējums energoefektivitātes pasākumu īstenošanai mājokļos.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pieejamais finansējums izmantots pilnībā – Altum daudzdzīvokļu māju energoefektivitātes programmas 2021–2027 līdzekļi 2025. gadā bija apgūti, tāpēc daļa ieinteresēto māju projektus nevarēja uzsākt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Daudzdzīvokļu ēku īpašnieki nespēj vienoties par kopīgu lēmumu pieņemšanu.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Informētība par problēmu ir pieaugusi arī institūciju pārstāvju vidū. Nav strukturālu pārmaiņu, bet vienošanās trūkums ir mazāks šķērslis nekā finanšu ierobežojumi valsts līmenī.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Zema iedzīvotāju informētība par siltumenerģijas taupīšanu un pareizu renovēto ēku, tai skaitā iekārtu, lietošanu. Informatīvo pasākumu organizēšana.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Informatīvo pasākumu un resursu klāsts ir ievērojami pieaudzis. Tomēr nav pietiekami pieejama lokāla informācija par katras ēkas stāvokli un uzlabojumiem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Garš (&gt;30 gadi) daudzdzīvokļu ēku atjaunošanas projektu atmaksāšanās periods, ja projektu rentabilitāte tiek balstīta tikai uz siltumenerģijas ietaupījumu un neņem vērā papildu ieguvumus no ēku atjaunošanas.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Finanšu jomā neatrisināts jautājums ir kapitāla izmaksas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nepietiekama būvniecības nozares kapacitāte, lai īsā laikā atjaunotu lielu skaitu daudzdzīvokļu ēku.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Nav rasts risinājums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atbalsta programmas mājokļu atjaunošanai ir fragmentētas un īslaicīgas. Lai saņemtu finansiālu atbalstu, projekta īstenotāji saskaras ar sarežģītu un laikietilpīgu dokumentācijas kārtošanu un birokrātiskiem procesiem.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Nav rasts risinājums, bet ir uzlabojumi birokrātiskajos procesos. REA galvenais ieguldījums ir tehniskās palīdzības sniegšana un konsultāciju darbs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ēku īpašnieku uzkrājumi ir nepietiekami, un nereti parādsaistības apgrūtina finansējuma saņemšanu atjaunošanai. Namu energoefektivitātes uzlabojumi nav veikti pienācīgā apjomā, neskatoties uz to, ka tam ir pieejami dažādi ES finanšu resursi.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ES finanšu resursu pieejamība ir nepietiekama un pastāv neziņa par turpmāko attīstību.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>dz</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nepieciešama strauja, ilgtspējīga, aprites ekonomikas principos balstīta ēku atjaunošana.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Joprojām nav viegli īstenojama risinājuma, kas ļautu mērogot izmaksu ziņā pieejamu atjaunošanu. Tiek vērtētas standartizācijas iespējas – industriālie paneļi, kvartālu pieeja u. c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Būtiska ietekme klimatneitralitātes sasniegšanā (otrs lielākais CO₂ emisiju avots).</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Izaicinājums nav mazinājies, tomēr sasniegts progress gan siltumenerģijas, gan elektroenerģijas jomās. Enerģijas ražošanas attīstībā pilsētā pašvaldības infrastruktūrai nav izšķirošas lomas – to nosaka privātais un valsts sektors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Nav skaidras un vienotas stratēģijas, kā panākt klimatneitralitāti enerģijas ražošanā Rīgas pilsētā.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tiek izstrādāta CSS attīstības stratēģija 2026.–2040. gadam (2. redakcija). 2025. gadā apstiprināts arī Rīgas Klimata līgums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Valsts nozīmes energoavotu ietekme (AS “Latvenergo” TEC-1 un TEC-2 darbība).</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Nav izmaiņu – TEC atrašanās Rīgā nosaka zemo AER īpatsvaru vietējā elektroenerģijas ražošanā.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Atbalsta trūkums elektroenerģijas ražošanai no AER (t. sk. koģenerācijas staciju OI atļaujas termiņa beigas un ietekme uz AER īpatsvaru).</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pašvaldībai nav iespējas noteikt nacionālas nozīmes enerģētikas infrastruktūras attīstību tiešā veidā. Ir pieņemta Latvijas enerģētikas stratēģija līdz 2050. gadam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Trūkst vienotas izpratnes par plašākas biomasas izmantošanu enerģijas ražošanā un tās ietekmi uz gaisa kvalitāti Rīgas pilsētā.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Biomasas izmantošanas scenārijus apskata CSS stratēģija un Nacionālais enerģētikas un klimata plāns. Decentralizētās siltumapgādes jomā apkures iekārtu maiņai tiek veidotas atbalsta programmas ar līdzfinansējumu – saistībā ar gaisa kvalitātes mērķiem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Augsts fosilo kurināmo īpatsvars – 69 % siltumenerģijas ražošanā un piegādē Rīgas pilsētas CSS.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AER īpatsvars CSS pieaudzis līdz 47 % (2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AER projektu konkurētspēja ar dabasgāzes tehnoloģiskajiem risinājumiem siltumenerģijas ražošanai.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Stratēģijas izstrādē 2026. gadā veikta ekonomisko faktoru analīze. Pieaug nozares interese par elektrifikāciju.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Augstāks administratīvais un vides prasību slogs, salīdzinot ar decentralizētās enerģijas ražošanas risinājumiem.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Situācija analizēta AS “Rīgas siltums” ilgtspējas pārskatos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pakāpeniska pāreja uz 4. paaudzes siltumapgādes sistēmu – vietās ar jau esošiem siltumtīkliem un siltumapgādes sistēmu.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pagaidām notiek atsevišķu pilotu mērogā, bet pieaug speciālistu zināšanas un kapacitāte tālāko projektu attīstībā.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AS “Rīgas siltums” mazo dabasgāzes katlu māju (ar kopējo uzstādīto jaudu 29,5 MW) tehniskais stāvoklis un turpmākā attīstība – pāreja uz AER un pieslēgšanās iespēja Rīgas pilsētas CSS.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Uzstādītas trīs saules stacijas (463,74 kW); AER risinājumus plānots ieviest, kur tas ir tehniski un ekonomiski pamatoti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Enerģijas pārpalikuma izmantošana – tehnoloģisko parametru nodrošinājums tā ievadei Rīgas CSS.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Notiek atlikumsiltuma izmantošanas izpēte un pilotēšana sadarbībā ar REA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Izejas datu pieejamība, kvalitāte un lietojums lēmumu pieņemšanai un turpmākam monitoringam.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Stratēģijas izstrādē dati ir aktualizēti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Informācijas un izejas datu pieejamība, ticamība un lietojums lēmumu pieņemšanā par decentralizēto siltumapgādi Rīgas pilsētā.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Izveidots apkures katlu reģistrs (13 464 ēkas), datu kvalitāte vēl netiek kontrolēta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Augsts decentralizētās siltumapgādes īpatsvars Rīgas pilsētā (44 %).</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Arvien problemātiskākais aspekts. Decentralizētās siltumapgādes īpatsvars samazinājies līdz 42,7 % (2025), taču AER īpatsvars tajā nepieaug (34,2 %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Augsts (63 %) fosilā kurināmā īpatsvars ražošanas un pakalpojumu sektorā un mājokļu sektorā (61 %).</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pakāpeniski pieaug bezemisiju tehnoloģiju izmantošana, arvien pastāv ekonomiski šķēršļi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Uzstādīto decentralizēto kurināmā sadedzināšanas iekārtu efektivitāte un atbilstība energoefektivitātes un citām normatīvo aktu prasībām (piem., ugunsdrošības prasību ievērošana).</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Problēmas nav atrisinātas, bet pozitīva ietekme ir atbalsta programmām mājsaimniecībās un uzņēmumos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Koksnes energoresursu (īpaši malkas) racionāla izmantošana.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sasaiste ar gaisa kvalitātes pasākumiem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gaisa piesārņojums no decentralizētām kurināmā sadedzināšanas iekārtām, īpaši Rīgas centrā.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sasaiste ar gaisa kvalitātes pasākumiem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Izaicinājumi elektroapgādē</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Augsts fosilā kurināmā īpatsvars (96 %) vietējās elektroenerģijas ražošanā.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AER īpatsvars vietējā ražošanā – 6,7 % (2025), atkarīgs no nacionālas nozīmes infrastruktūras darbības.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Izaicinājumi elektroapgādē</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>REA nav datu uzskaites sistēmas par ieviestajiem AER projektiem, un netiek apkopoti un analizēti dati par uzstādītajām jaudām vai saražoto elektroenerģiju.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Datus par saules paneļu jaudu pilsētā sniedz Sadales tīkls. Centrālā statistikas pārvalde veido rādītāju par juridisku personu tīklā nodoto saules enerģiju.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Izaicinājumi elektroapgādē</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Energokopienu veidošana, AER iekārtu uzstādīšanas veicināšana vietējai un individuālai elektroenerģijas ražošanai.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Regulējums ir neizdevīgs; Rīgā 2025. gadā tika izveidota viena energokopiena, bet tās darbība ir ierobežota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Izaicinājumi elektroapgādē</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Pāreja uz elektrotransportu un siltumapgādes sistēmas elektrifikāciju. Pāreja no gāzes izmantošanas uz elektroenerģiju ēst gatavošanai ēkās.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Elektrifikācija pieaug; tīkla jaudas Rīgā ir pieejamas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Izaicinājumi elektroapgādē</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Jaunu saules PV izveide dažādās jaunattīstītajās zonās.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Aktivitāte notiek dzīvojamo ēku jaunbūvju un komerciālajā sektorā.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Izaicinājumi dabasgāzes apgādē</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dabasgāzes patēriņa datu pieejamība par visām patērētāju grupām, lai plānotu mērķētas rīcības (91 % no kopējā dabasgāzes patēriņa veido kategorija “Pārējie”).</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Datu pieejamības ierobežojumi nav atrisināti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Izaicinājumi dabasgāzes apgādē</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Dabasgāzes patēriņa samazināšana visos sektoros.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Rādītāji liecina par mērenu dabasgāzes patēriņa samazinājumu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Izaicinājumi dabasgāzes apgādē</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Lieli zudumi pie dabasgāzes galapatērētājiem. Dzīvojamo un komerciālo ēku gāzes apgādes sistēmas elementu neatbilstība normatīvajām prasībām.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plašāka informācija sniegta AS “Gaso” ilgtspējas pārskatā.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Izaicinājumi dabasgāzes apgādē</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Rīgas ilgtspējīgas attīstības stratēģijā paredzēts nodrošināt vairākus apbūves rajonus ar gāzes apgādi, kas nesakrīt ar klimatneitralitātes redzējumu – būtu jāmeklē citi apkures risinājumi (piem., pieslēgums CSS, siltumenerģijas patēriņa samazināšana).</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>Nepieciešama papildu informācija.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>pas</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Pašvaldības transporta sektors</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Apzinātu pašvaldības iestāžu autoparku, sistemātiski apkopotu datu par degvielas patēriņu, transportlīdzekļu nobraukumu trūkums; sistēmas datu regulārai atjaunošanai un analīzei trūkums</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Uzskaiti veic Finanšu departaments. Nav ieviesta vienota sistēma autoparka izmantošanas plānošanai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>pas</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Pašvaldības transporta sektors</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Finansējuma pieejamība alternatīvās degvielas transportlīdzekļu (īpaši bezemisiju) skaita būtiskai palielināšanai pašvaldības autoparkā</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Elektroauto skaits ir pieaudzis gan administrācijas, gan kapitālsabiedrību autoparkā. Tomēr nav vienota risinājuma visa autoparka nomaiņai, ieskaitot lielākas noslodzes transportlīdzekļus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>pas</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Pašvaldības transporta sektors</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Vāja transportlīdzekļu izmantošanas efektivitāte (neefektīvs nobraukums)</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Nav vienotas uzskaites pašvaldības mērogā, bet iespējama atšķirīga situācija dažādu organizāciju ietvaros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Izejas datu pieejamība un ticamība daudzdzīvokļu ēku energoefektivitātes līmeņa izvērtējumam.</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Ierobežojumi joprojām pastāv, tomēr pārskata periodā sasniegts būtisks progress energoefektivitātes datu jomā – ĢeoRīga tematiskās kartes, energosertifikāti, datu publicēšana un apmaiņa ar citām institūcijām.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Lielākais siltumenerģijas patēriņš un CO₂ emisiju avots Rīgas pilsētas CSS.</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Nav notikušas būtiskas pārmaiņas. Aktīvāku lomu uzņemas siltumapgādes sistēmas operators un māju apsaimniekošanas uzņēmumi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Dzīvojamās ēkas ir gan fiziski, gan morāli novecojušas, un revitalizācijas pasākumi netiek veikti pietiekamā apjomā.</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājums nav mazinājies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr"/>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Zems atjaunoto daudzdzīvokļu ēku īpatsvars (1,4 % jeb 159 ēkas). Iedzīvotāju zemā interese par daudzdzīvokļu ēku atjaunošanu.</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Atjaunoto ēku kopskaits joprojām ir mazs (209 ēkas 2025. gadā), taču iedzīvotāju interese ir pieaugusi – dominē finanšu un administratīvie šķēršļi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr"/>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Nav izstrādāta daudzdzīvokļu ēku atjaunošanas stratēģija, pašvaldības līmenī nav noteikta atbildīgā iestāde, kura sistemātiski risinātu šos jautājumus.</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>2026. gadā notiek Ēku atjaunošanas plāna izstrāde, kas ir priekšnoteikums arī pašvaldības līmeņa stratēģijas definēšanai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr"/>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Pašvaldības namu apsaimniekotāja sliktā reputācija ēku atjaunošanas projektu organizēšanā.</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Rīgas namu pārvaldnieka darbā panākti uzlabojumi. Ar Privatizācijas pabeigšanas likumu (spēkā no 2025. gada 1. maija) māju īpašniekiem jāpārņem pārvaldīšanas tiesības, un pašvaldība nolēmusi izbeigt līdzdalību uzņēmumā.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr"/>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Daudzdzīvokļu ēku ar nelielu dzīvokļu skaitu atjaunošana, kas ir tehniski sliktā stāvoklī jeb ekspluatācijai bīstamās ēkas. Piem., divstāvu koka apbūves ēkas Maskavas forštatē, Vecmīlgrāvī, Sarkandaugavā, Vecpilsētā un Centra rajonā.</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Atsevišķi labi piemēri, bet vispārēja risinājuma nav.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr"/>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Daudzdzīvokļu ēku atjaunošana, kas atbilst kultūras pieminekļu statusam.</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Atsevišķi labi piemēri.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr"/>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Daudzdzīvokļu ēku īpašnieku biedrību loma ēku atjaunošanā ir būtiska. Zema iedzīvotāju aktivitāte, kas ierobežo biedrību dibināšanu. Nav zināms kopējais biedrību skaits un sarežģīta to identificēšana.</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Ir mainīts normatīvais regulējums, paredzot alternatīvu biedrību dibināšanai – lēmumu pieņemšanu dzīvokļu īpašnieku kopībā.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr"/>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Individuālās siltumenerģijas uzskaites sistēmas izveide līdz 2027. gadam.</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Ieviešanas progress atšķiras atkarībā no ēkas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr"/>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Netiek pietiekami aktīvi izmantots pieejamais līdzfinansējums energoefektivitātes pasākumu īstenošanai mājokļos.</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Pieejamais finansējums izmantots pilnībā – Altum daudzdzīvokļu māju energoefektivitātes programmas 2021–2027 līdzekļi 2025. gadā bija apgūti, tāpēc daļa ieinteresēto māju projektus nevarēja uzsākt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr"/>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Daudzdzīvokļu ēku īpašnieki nespēj vienoties par kopīgu lēmumu pieņemšanu.</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Informētība par problēmu ir pieaugusi arī institūciju pārstāvju vidū. Nav strukturālu pārmaiņu, bet vienošanās trūkums ir mazāks šķērslis nekā finanšu ierobežojumi valsts līmenī.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr"/>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Zema iedzīvotāju informētība par siltumenerģijas taupīšanu un pareizu renovēto ēku, tai skaitā iekārtu, lietošanu. Informatīvo pasākumu organizēšana.</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Informatīvo pasākumu un resursu klāsts ir ievērojami pieaudzis. Tomēr nav pietiekami pieejama lokāla informācija par katras ēkas stāvokli un uzlabojumiem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr"/>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Garš (&gt;30 gadi) daudzdzīvokļu ēku atjaunošanas projektu atmaksāšanās periods, ja projektu rentabilitāte tiek balstīta tikai uz siltumenerģijas ietaupījumu un neņem vērā papildu ieguvumus no ēku atjaunošanas.</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Finanšu jomā neatrisināts jautājums ir kapitāla izmaksas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr"/>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Nepietiekama būvniecības nozares kapacitāte, lai īsā laikā atjaunotu lielu skaitu daudzdzīvokļu ēku.</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Nav rasts risinājums.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr"/>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Atbalsta programmas mājokļu atjaunošanai ir fragmentētas un īslaicīgas. Lai saņemtu finansiālu atbalstu, projekta īstenotāji saskaras ar sarežģītu un laikietilpīgu dokumentācijas kārtošanu un birokrātiskiem procesiem.</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Nav rasts risinājums, bet ir uzlabojumi birokrātiskajos procesos. REA galvenais ieguldījums ir tehniskās palīdzības sniegšana un konsultāciju darbs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr"/>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Ēku īpašnieku uzkrājumi ir nepietiekami, un nereti parādsaistības apgrūtina finansējuma saņemšanu atjaunošanai. Namu energoefektivitātes uzlabojumi nav veikti pienācīgā apjomā, neskatoties uz to, ka tam ir pieejami dažādi ES finanšu resursi.</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>ES finanšu resursu pieejamība ir nepietiekama un pastāv neziņa par turpmāko attīstību.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>dz</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr"/>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Nepieciešama strauja, ilgtspējīga, aprites ekonomikas principos balstīta ēku atjaunošana.</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Joprojām nav viegli īstenojama risinājuma, kas ļautu mērogot izmaksu ziņā pieejamu atjaunošanu. Tiek vērtētas standartizācijas iespējas – industriālie paneļi, kvartālu pieeja u. c.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Būtiska ietekme klimatneitralitātes sasniegšanā (otrs lielākais CO₂ emisiju avots).</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājums nav mazinājies, tomēr sasniegts progress gan siltumenerģijas, gan elektroenerģijas jomās. Enerģijas ražošanas attīstībā pilsētā pašvaldības infrastruktūrai nav izšķirošas lomas – to nosaka privātais un valsts sektors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Nav skaidras un vienotas stratēģijas, kā panākt klimatneitralitāti enerģijas ražošanā Rīgas pilsētā.</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Tiek izstrādāta CSS attīstības stratēģija 2026.–2040. gadam (2. redakcija).
-2025. gadā apstiprināts arī Rīgas Klimata līgums.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Valsts nozīmes energoavotu ietekme (AS “Latvenergo” TEC-1 un TEC-2 darbība).</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Nav izmaiņu – TEC atrašanās Rīgā nosaka zemo AER īpatsvaru vietējā elektroenerģijas ražošanā.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Atbalsta trūkums elektroenerģijas ražošanai no AER (t. sk. koģenerācijas staciju OI atļaujas termiņa beigas un ietekme uz AER īpatsvaru).</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Pašvaldībai nav iespējas noteikt nacionālas nozīmes enerģētikas infrastruktūras attīstību tiešā veidā. Ir pieņemta Latvijas enerģētikas stratēģija līdz 2050. gadam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi enerģijas ražošanas sektorā</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Trūkst vienotas izpratnes par plašākas biomasas izmantošanu enerģijas ražošanā un tās ietekmi uz gaisa kvalitāti Rīgas pilsētā.</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Biomasas izmantošanas scenārijus apskata CSS stratēģija un Nacionālais enerģētikas un klimata plāns. Decentralizētās siltumapgādes jomā apkures iekārtu maiņai tiek veidotas atbalsta programmas ar līdzfinansējumu – saistībā ar gaisa kvalitātes mērķiem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Augsts fosilo kurināmo īpatsvars – 69 % siltumenerģijas ražošanā un piegādē Rīgas pilsētas CSS.</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>AER īpatsvars CSS pieaudzis līdz 47 % (2025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>AER projektu konkurētspēja ar dabasgāzes tehnoloģiskajiem risinājumiem siltumenerģijas ražošanai.</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Stratēģijas izstrādē 2026. gadā veikta ekonomisko faktoru analīze. Pieaug nozares interese par elektrifikāciju.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Augstāks administratīvais un vides prasību slogs, salīdzinot ar decentralizētās enerģijas ražošanas risinājumiem.</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Situācija analizēta AS “Rīgas siltums” ilgtspējas pārskatos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Pakāpeniska pāreja uz 4. paaudzes siltumapgādes sistēmu – vietās ar jau esošiem siltumtīkliem un siltumapgādes sistēmu.</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Pagaidām notiek atsevišķu pilotu mērogā, bet pieaug speciālistu zināšanas un kapacitāte tālāko projektu attīstībā.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>AS “Rīgas siltums” mazo dabasgāzes katlu māju (ar kopējo uzstādīto jaudu 29,5 MW) tehniskais stāvoklis un turpmākā attīstība – pāreja uz AER un pieslēgšanās iespēja Rīgas pilsētas CSS.</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Uzstādītas trīs saules stacijas (463,74 kW); AER risinājumus plānots ieviest, kur tas ir tehniski un ekonomiski pamatoti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Enerģijas pārpalikuma izmantošana – tehnoloģisko parametru nodrošinājums tā ievadei Rīgas CSS.</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Notiek atlikumsiltuma izmantošanas izpēte un pilotēšana sadarbībā ar REA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi centralizētajā siltumapgādes sistēmā</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Izejas datu pieejamība, kvalitāte un lietojums lēmumu pieņemšanai un turpmākam monitoringam.</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Stratēģijas izstrādē dati ir aktualizēti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Informācijas un izejas datu pieejamība, ticamība un lietojums lēmumu pieņemšanā par decentralizēto siltumapgādi Rīgas pilsētā.</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Izveidots apkures katlu reģistrs (13 464 ēkas), datu kvalitāte vēl netiek kontrolēta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Augsts decentralizētās siltumapgādes īpatsvars Rīgas pilsētā (44 %).</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Arvien problemātiskākais aspekts. Decentralizētās siltumapgādes īpatsvars samazinājies līdz 42,7 % (2025), taču AER īpatsvars tajā nepieaug (34,2 %).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Augsts (63 %) fosilā kurināmā īpatsvars ražošanas un pakalpojumu sektorā un mājokļu sektorā (61 %).</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Pakāpeniski pieaug bezemisiju tehnoloģiju izmantošana, arvien pastāv ekonomiski šķēršļi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Uzstādīto decentralizēto kurināmā sadedzināšanas iekārtu efektivitāte un atbilstība energoefektivitātes un citām normatīvo aktu prasībām (piem., ugunsdrošības prasību ievērošana).</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Problēmas nav atrisinātas, bet pozitīva ietekme ir atbalsta programmām mājsaimniecībās un uzņēmumos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Koksnes energoresursu (īpaši malkas) racionāla izmantošana.</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Sasaiste ar gaisa kvalitātes pasākumiem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi decentralizētajā siltumapgādē</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Gaisa piesārņojums no decentralizētām kurināmā sadedzināšanas iekārtām, īpaši Rīgas centrā.</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Sasaiste ar gaisa kvalitātes pasākumiem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi elektroapgādē</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Augsts fosilā kurināmā īpatsvars (96 %) vietējās elektroenerģijas ražošanā.</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>AER īpatsvars vietējā ražošanā – 6,7 % (2025), atkarīgs no nacionālas nozīmes infrastruktūras darbības.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi elektroapgādē</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>REA nav datu uzskaites sistēmas par ieviestajiem AER projektiem, un netiek apkopoti un analizēti dati par uzstādītajām jaudām vai saražoto elektroenerģiju.</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Datus par saules paneļu jaudu pilsētā sniedz Sadales tīkls. Centrālā statistikas pārvalde veido rādītāju par juridisku personu tīklā nodoto saules enerģiju.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi elektroapgādē</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Energokopienu veidošana, AER iekārtu uzstādīšanas veicināšana vietējai un individuālai elektroenerģijas ražošanai.</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Regulējums ir neizdevīgs; Rīgā 2025. gadā tika izveidota viena energokopiena, bet tās darbība ir ierobežota.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi elektroapgādē</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Pāreja uz elektrotransportu un siltumapgādes sistēmas elektrifikāciju. Pāreja no gāzes izmantošanas uz elektroenerģiju ēst gatavošanai ēkās.</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Elektrifikācija pieaug; tīkla jaudas Rīgā ir pieejamas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi elektroapgādē</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Jaunu saules PV izveide dažādās jaunattīstītajās zonās.</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Aktivitāte notiek dzīvojamo ēku jaunbūvju un komerciālajā sektorā.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi elektroapgādē</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Uzņēmumu veicināšana pārejai uz vietējo elektroenerģijas ražošanu pašpatēriņam.</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi dabasgāzes apgādē</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Dabasgāzes patēriņa datu pieejamība par visām patērētāju grupām, lai plānotu mērķētas rīcības (91 % no kopējā dabasgāzes patēriņa veido kategorija “Pārējie”).</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Datu pieejamības ierobežojumi nav atrisināti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi dabasgāzes apgādē</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Dabasgāzes patēriņa samazināšana visos sektoros.</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Rādītāji liecina par mērenu dabasgāzes patēriņa samazinājumu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi dabasgāzes apgādē</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Lieli zudumi pie dabasgāzes galapatērētājiem. Dzīvojamo un komerciālo ēku gāzes apgādes sistēmas elementu neatbilstība normatīvajām prasībām.</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Plašāka informācija sniegta AS “Gaso” ilgtspējas pārskatā.</t>
-        </is>
-      </c>
-    </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Izaicinājumi dabasgāzes apgādē</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Rīgas ilgtspējīgas attīstības stratēģijā paredzēts nodrošināt vairākus apbūves rajonus ar gāzes apgādi, kas nesakrīt ar klimatneitralitātes redzējumu – būtu jāmeklē citi apkures risinājumi (piem., pieslēgums CSS, siltumenerģijas patēriņa samazināšana).</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Nepieciešama papildu informācija.</t>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>tr</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Pārvietošanās nepieciešamības mazināšana (Rīgas iedzīvotāju un Rīgā iebraucošo Pierīgas pašvaldību iedzīvotāju vidū).</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Nav kompleksa risinājuma. Attālinātā darba ietekme ir netieša.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr"/>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Pārvietošanās nepieciešamības mazināšana (Rīgas iedzīvotāju un Rīgā iebraucošo Pierīgas pašvaldību iedzīvotāju vidū).</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Nav kompleksa risinājuma. Attālinātā darba ietekme ir netieša.</t>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Palielināt braucienu skaitu, kas veikti ar kājām, velosipēdu un sabiedrisko transportu; samazināt braucienu skaitu, kas veikti ar automašīnu.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sabiedriskā transporta pasažieru skaits pieaug (114,74 milj. 2023. gadā, 118,5 milj. 2025. gadā), tomēr nav pasākumu ar izmērāmu ietekmi uz pārvietošanās veidu sadalījumu. 2025. gada aptaujā 48 % Rīgas iedzīvotāju regulāri brauca ar automašīnu un 51 % regulāri izmantoja sabiedrisko transportu.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr"/>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Palielināt braucienu skaitu, kas veikti ar kājām, velosipēdu un sabiedrisko transportu; samazināt braucienu skaitu, kas veikti ar automašīnu.</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Sabiedriskā transporta pasažieru skaits pieaug (114,74 milj. 2023. gadā, 118,5 milj. 2025. gadā), tomēr nav pasākumu ar izmērāmu ietekmi uz pārvietošanās veidu sadalījumu.</t>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Uzlabot veloinfrastruktūru.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ir progress.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr"/>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>Uzlabot veloinfrastruktūru.</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Ir progress.</t>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Palielināt vidējo braucēju skaitu automašīnās.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Nav datu.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr"/>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Palielināt vidējo braucēju skaitu automašīnās.</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Nav datu.</t>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Iedzīvotāju dzīves veida paradumu maiņa.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Atsevišķas fokusgrupas, kampaņas.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr"/>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Iedzīvotāju dzīves veida paradumu maiņa.</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Atsevišķas fokusgrupas, kampaņas.</t>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Drošas un ērtas veloinfrastruktūras un gājēju infrastruktūras straujāka attīstība.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Veloceļu garums kopš 2020. gada pieaudzis par 69 %; jauni projekti īstenoti arī 2025. un 2026. gadā.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr"/>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Drošas un ērtas veloinfrastruktūras un gājēju infrastruktūras straujāka attīstība.</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Veloceļu garums kopš 2020. gada pieaudzis par 69 %; jauni projekti īstenoti arī 2025. un 2026. gadā.</t>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Atjaunīgās enerģijas īpatsvara palielināšana sabiedriskā transporta autoparkā atbilstoši Transporta enerģijas likuma prasībām.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Transporta enerģijas likums pieņemts 2025. gada 27. novembrī un stājies spēkā 2026. gada 1. janvārī. “Rīgas satiksmes” autoparkā pieaug bezemisiju transportlīdzekļu īpatsvars – 2025. gadā tie veidoja 51 % autoparka, un elektroautobusu skaits pieaudzis no 23 (2023) līdz 52 (2025). Vienlaikus autobusu nobraukumā joprojām dominē dīzeļdegviela – elektroautobusi veica 8,1 % autobusu kilometru.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr"/>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Atjaunīgās enerģijas īpatsvara palielināšana sabiedriskā transporta autoparkā atbilstoši Transporta enerģijas likuma prasībām.</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Transporta enerģijas likums pieņemts 2025. gada 27. novembrī un stājies spēkā 2026. gada 1. janvārī. “Rīgas satiksmes” autoparkā pieaug bezemisiju transportlīdzekļu īpatsvars – 2025. gadā tie veidoja 51 % autoparka, un elektroautobusu skaits pieaudzis no 23 (2023) līdz 52 (2025). Vienlaikus autobusu nobraukumā joprojām dominē dīzeļdegviela – elektroautobusi veica 8,1 % autobusu kilometru.</t>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Nepietiekami izmantots dzelzceļa transports pasažieru pārvadājumiem pilsētas robežās.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Uzlabojums pēc jauno pasažieru vilcienu atklāšanas. Plānota bateriju vilcienu ieviešana.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr"/>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Nepietiekami izmantots dzelzceļa transports pasažieru pārvadājumiem pilsētas robežās.</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Uzlabojums pēc jauno pasažieru vilcienu atklāšanas. Plānota bateriju vilcienu ieviešana.</t>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Alternatīvo degvielu infrastruktūras attīstība, t. sk. elektrouzlādes stacijas Rīgas apkaimēs.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pašvaldība rīkojusi izsoli uzlādes staciju izbūvei apkaimēs (90 pieslēgvietas); 2023. gadā izstrādāta uzlādes infrastruktūras tīkla attīstības koncepcija, un tiek izstrādāta lēnās uzlādes koncepcija. Pieejamība teritoriāli fragmentēta.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr"/>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Alternatīvo degvielu infrastruktūras attīstība, t. sk. elektrouzlādes stacijas Rīgas apkaimēs.</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Pašvaldība rīkojusi izsoli uzlādes staciju izbūvei apkaimēs (90 pieslēgvietas); 2023. gadā izstrādāta uzlādes infrastruktūras tīkla attīstības koncepcija, un tiek izstrādāta lēnās uzlādes koncepcija. Pieejamība teritoriāli fragmentēta.</t>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Autoparka vidējā vecuma samazināšana.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Nav tiešas pilsētas ietekmes privātajā sektorā, nepieciešamas lielākas investīcijas sabiedriskajā transportā.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr"/>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>Autoparka vidējā vecuma samazināšana.</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Nav tiešas pilsētas ietekmes privātajā sektorā, nepieciešamas lielākas investīcijas sabiedriskajā transportā.</t>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sabiedriskā transporta lietotāju skaita samazinājums un privāto automašīnu lietotāju skaita pieaugums COVID-19 ietekmē.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pasažieru skaits pakāpeniski atjaunojas – 114,74 milj. (2023), 115,97 milj. (2024) un 118,5 milj. (2025). Pakalpojuma pievilcību uzlabo maršrutu tīkla pārkārtošana, jauni tramvaju savienojumi, nakts transporta pilotprojekts un vienotā biļete ar “Pasažieru vilcienu”. Pirms COVID-19 līmenis (134,4 milj. pasažieru 2019. gadā) vēl nav sasniegts. https://stat.gov.lv/lv/statistikas-temas/noz/pasazieru-parvadajumi/cits/8896-apsekojuma-latvijas-iedzivotaju-mobilitate?themeCode=TP</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr"/>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Sabiedriskā transporta lietotāju skaita samazinājums un privāto automašīnu lietotāju skaita pieaugums COVID-19 ietekmē.</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Pasažieru skaits pakāpeniski atjaunojas – 114,74 milj. (2023), 115,97 milj. (2024) un 118,5 milj. (2025). Pakalpojuma pievilcību uzlabo maršrutu tīkla pārkārtošana, jauni tramvaju savienojumi, nakts transporta pilotprojekts un vienotā biļete ar “Pasažieru vilcienu”.
-https://stat.gov.lv/lv/statistikas-temas/noz/pasazieru-parvadajumi/cits/8896-apsekojuma-latvijas-iedzivotaju-mobilitate?themeCode=TP</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>tr</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr"/>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Sistēmas izveide regulārai datu/informācijas vākšanai iedzīvotāju mobilitātes parametru monitorēšanai (mobilitātes aptaujas, transportlīdzekļu skaitīšana).</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Aptaujas tiek veiktas, bet varētu biežāk.</t>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Aptaujas tiek veiktas, bet varētu biežāk. 2025. gadā PAD pētījumā veikta iedzīvotāju aptauja (n = 2500) un analizēti e-talonu un GTFS dati, taču braucienos balstīta mobilitātes aptauja nav atkārtota kopš 2019. gada.</t>
         </is>
       </c>
     </row>
@@ -5556,345 +5465,345 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>EPS attīstība, pāreja uz ikstundas datu monitoringu un datu apmaiņa.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Darbinieku iesaistes lietotnes pilotprojekts 5–7 ēkās, samazinot patēriņu ārpus darba laika.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Siltumenerģijas un elektroenerģijas iepirkumu nosacījumu pilnveidošana.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Pašvaldības ēku modernizācija – dabasgāzes katlu nomaiņa.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Sadarbība ar citām struktūrvienībām un ēku pārvaldniekiem.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Saules paneļu projektu īstenošana pašvaldības ēkās (10 Modernizācijas fonda projektu pieteikumi).</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Saules paneļu projektu īstenošana pašvaldības ēkās (Modernizācijas fonda projektu pieteikumi).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>pas</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ūdens patēriņa ierīču audits un priekšlikumi ierīču nomaiņai.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>REA ēku grupas kapacitātes uzturēšana un komandas izaugsme.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Rīgas energoefektivitātes fonda modeļa gala izvērtējums, lēmumu pieņemšana.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Kvartāla atjaunošanas vadlīniju pabeigšana un pielietojums praksē.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Tehniskās palīdzības un iedzīvotāju konsultāciju projekta turpinājums, finansējums pēc 2027. gada.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Ēku informācijas un energoefektivitātes datu jomas attīstība, īpaši decentralizētās siltumapgādes segmentā.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Esošo kvartālu atjaunošanas pilotu monitorings un atbalsts.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Sadarbība ar citām struktūrvienībām un organizācijām mērķu īstenošanā (Īpašuma departaments u. c.).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Pilotprojekti siltumapgādes, energokopienu jomā – atjaunīgo energoresursu integrācija ēkās.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Pasākumi, kas vērsti uz gaisa kvalitātes uzlabošanu un enerģētiskās nabadzības mazināšanu.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>dz</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Mājokļu energoapgādes zaļināšana individuālo dzīvojamo māju apbūves teritorijās.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>CSS attīstības stratēģijas 2026.–2040. gadam apspriešana darba grupā, sabiedriskā apspriešana un iesniegšana apstiprināšanai Rīgas domē.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Apkures katlu reģistra papildināšana ar CSS un dabasgāzes tīklam pieslēgtajām ēkām.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Atlikumsiltuma izmantošanas izpēte un pilotēšana sadarbībā ar AS “Rīgas siltums”.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Savstarpējā koordinācija ar pasākumiem gaisa kvalitātes uzlabošanas jomā.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Sadarbības stiprināšana ar PAD, ĀMD un Rīgas digitālo aģentūru transporta un pilsētplānošanas projektu ietekmes novērtēšanai.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>SEG emisiju aprēķina metodikas pilnveidošana un funkcionalitātes iestrāde topošajā mobilitātes datu sistēmā.</t>
         </is>
@@ -5911,7 +5820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5939,8 +5848,8 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Rīgas kopējās CO₂ emisijas 2025. gadā bija 1 574 ktCO₂ – par 9,6 % mazāk nekā 2019. gadā (mērķis 2030. gadam: −30 %) un par 63,3 % mazāk nekā 1990. gadā (mērķis: −70 %). Progress līdz mērķim ir 32 %, tāpēc emisiju samazinājums atpaliek no trajektorijas.
-No 21 SECAP2030 mērķa, kam vidusposmā novērtēta izpilde, viens mērķis ir sasniegts, septiņi atbilst trajektorijai, deviņi atpaliek no trajektorijas un vienā mērķī progresa nav. Divu mērķu izpilde (luksoforu īpatnējais elektroenerģijas patēriņš un privāto automašīnu lietotāju īpatsvars) pagaidām netika apskatīta, savukārt siltumenerģijas zudumu mērķis netiek vērtēts, jo zudumi ir atkarīgi no klimatiskajiem apstākļiem un mērķis jāpārskata.
-Lai 2030. gada mērķus sasniegtu, pasākumu ieviešana jāpaātrina – īpaši ēku atjaunošanā, AER izmantošanā decentralizētajā siltumapgādē un elektroenerģijas ražošanā, kā arī privātā transporta emisiju mazināšanā. Vienlaikus jāstiprina plāna ieviešanas koordinācija, finansējuma plānošana un datu pārvaldība.</t>
+No 21 SECAP2030 mērķa, kam vidusposmā novērtēta izpilde, trīs mērķi ir sasniegti, seši atbilst trajektorijai, vienpadsmit atpaliek no trajektorijas. Viena mērķa izpilde (privāto automašīnu lietotāju īpatsvars) pagaidām netika apskatīta. Siltumenerģijas zudumu mērķis vidusposmā mainīts atbilstoši NEKP2030 pasākuma 3.1.3.11 rezultatīvajam rādītājam – tagad tiek vērtēti zudumi siltumtīklos aktīvajā apkures sezonā (&lt; 10 % līdz 2030. gadam).
+Lai 2030. gada mērķus sasniegtu, pasākumu ieviešana jāpaātrina – īpaši ēku atjaunošanā, AER izmantošanā decentralizētajā siltumapgādē, kā arī privātā transporta emisiju mazināšanā. Vienlaikus jāstiprina plāna ieviešanas koordinācija, finansējuma plānošana un datu pārvaldība.</t>
         </is>
       </c>
     </row>
@@ -5957,8 +5866,8 @@
 Šajā pārskatā apskatām sektorus – pašvaldības infrastruktūru, daudzdzīvokļu ēkas un enerģijas ražošanu –, kuru pasākumu koordinēšana galvenokārt ir Rīgas enerģētikas aģentūras (REA) pārziņā. Atsevišķa sadaļa veltīta arī transporta sektoram.
 Transporta joma ir lielākais Rīgas emisiju sektors un ir īpaši nozīmīgs klimata un enerģijas mērķu sasniegšanā. Tomēr ar šīs jomas mērķiem REA padziļināti nestrādā un pasākumu ieviešana gan stratēģijas, gan projektu līmenī lielākoties ir citu pašvaldības struktūrvienību pārziņā. Šīs jomas izvērtēšana jāturpina sadarbībā ar kolēģiem no mobilitātes, pilsētplānošanas un sabiedriskā transporta jomas.
 Šajā pārskatā plašāk netiek vērtētas četras SECAP2030 jomas: aprites ekonomika un atkritumu apsaimniekošana, pielāgošanās klimata pārmaiņām, vides komunikācija, kā arī klimatneitralitātes politika.
-Aprites ekonomikas rīcību jomas un rādītāji detalizētāk noteikti Rīgas aprites ekonomikas rīcības plānā, kas tika apstiprināts 2026. gada augustā.
-Rīgai nav izstrādāts atsevišķs plāns par pielāgošanos klimata pārmaiņām, bet šīs jomas riski un pasākumi daļēji iekļauti Rīgas pilsētvides zaļināšanas plānā, kura pirmā redakcija 2026. gada vasarā tika nodota sabiedriskajai apspriešanai. Pielāgošanās jomas datus REA pagaidām neapkopo, un atjaunotajā klimata un enerģētikas rādītāju sarakstā pielāgošanās rādītāji nav iekļauti, kamēr zaļināšanas plāna izstrāde nav noslēgusies. Plāna izstrādē jau veikta plūdu un karstumsalu risku kartēšana.
+Aprites ekonomikas rīcību jomas un rādītāji detalizētāk noteikti Rīgas valstspilsētas pašvaldības aprites ekonomikas rīcības plānā 2026.–2030. gadam, kas tika apstiprināts 2026. gada augustā.
+Rīgai nav izstrādāts atsevišķs plāns par pielāgošanos klimata pārmaiņām, bet šīs jomas riski un pasākumi daļēji iekļauti Rīgas pilsētvides zaļināšanas plānā 2027.–2031. gadam, kura pirmā redakcija 2026. gada vasarā tika nodota sabiedriskajai apspriešanai. Pielāgošanās jomas datus REA pagaidām neapkopo, un atjaunotajā klimata un enerģētikas rādītāju sarakstā pielāgošanās rādītāji nav iekļauti, kamēr zaļināšanas plāna izstrāde nav noslēgusies. Plāna izstrādē jau veikta plūdu un karstumsalu risku kartēšana.
 Vides komunikācijas pasākumi attiecas uz visiem pārējiem sektoriem, bet nav tieši saistīti ar CO2 emisiju apjoma vai fosilo energoresursu patēriņa rādītājiem. Tā kā komunikācijas jomas aktivitātes vērtējamas ar citām metodēm, šo sadaļu plānots apskatīt atsevišķi 2027. gadā.
 Rīgas SECAP2030 vidusposma pārskata saturs sadalīts pa četriem sektoriem. Katram sektoram sniegta informācija par mērķu izpildes statusu, rādītāju vērtībām, komentārs par pasākumu ieviešanu un izaicinājumiem, kā arī uzskaitīti nākamie soļi.</t>
         </is>
@@ -5972,7 +5881,9 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mērķu izpildes statuss noteikts, salīdzinot 2025. gada vērtību ar lineāru trajektoriju no bāzes gada (2019. vai 2020. gads) līdz 2030. gada mērķa vērtībai. Progress izteikts kā līdz 2025. gadam sasniegtā izmaiņa procentos no kopējās nepieciešamās izmaiņas. Lineārai trajektorijai 2025. gadā atbilst 54,5 % (bāzes gads 2019) vai 50 % (bāzes gads 2020) progress. Mērķis atbilst trajektorijai, ja progress ir ne vairāk kā 10 procentpunktus zem šīs vērtības, t. i., vismaz 44,5 % vai 40 %. Ja progress ir pozitīvs, bet zemāks, mērķis atpaliek no trajektorijas; ja rādītājs nav uzlabojies, norādīts “nav progresa”. Mērķis ir sasniegts, ja progress ir 100 %.</t>
+          <t>Mērķu izpildes statuss noteikts, salīdzinot 2025. gada vērtību ar lineāru trajektoriju no bāzes gada (2019. vai 2020. gads) līdz 2030. gada mērķa vērtībai. Progress izteikts kā līdz 2025. gadam sasniegtā izmaiņa procentos no kopējās nepieciešamās izmaiņas. Lineārai trajektorijai 2025. gadā atbilst 54,5 % (bāzes gads 2019) vai 50 % (bāzes gads 2020) progress. Mērķis atbilst trajektorijai, ja progress ir ne vairāk kā 10 procentpunktus zem šīs vērtības, t. i., vismaz 44,5 % vai 40 %. Ja progress ir zemāks, mērķis atpaliek no trajektorijas (arī tad, ja rādītājs nav uzlabojies). Mērķis ir sasniegts, ja progress ir 100 %.
+Vidusposma novērtējuma sagatavošanā pielietotās metodes un avoti: konsultācijas ar REA ekspertiem atbilstoši darbības jomām; konsultācijas ar pašvaldības departamentu vai kapitālsabiedrību pārstāvjiem; informācija Rīgas pašvaldības institūciju mājaslapā; kapitālsabiedrību publiskie pārskati; publiskie informācijas avoti rādītāju precizēšanai; rādītāju pārskatīšana, vērtību atjaunošana un apraksts; aprēķini.
+Pārskatu veido trīs daļas: teksta pārskats (.docx), rādītāju un mērķu tabula (.xlsx) un tīmekļa vietne.</t>
         </is>
       </c>
     </row>
@@ -5985,64 +5896,39 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Vidusposmā SECAP2030 īstenošana kopumā virzās pareizajā virzienā, taču pārāk lēni, lai līdz 2030. gadam sasniegtu galvenos CO₂ emisiju samazināšanas mērķus. Rīgas kopējās CO₂ emisijas 2025. gadā bija par 9,6 % zemākas nekā 2019. gadā, bet mērķis ir −30 %. Lai to sasniegtu, atlikušajos piecos gados emisijas būtu jāsamazina vidēji par aptuveni 71 ktCO₂ gadā – aptuveni 2,5 reizes straujāk nekā laikā no 2019. līdz 2025. gadam.
-Labākie rezultāti sasniegti jomās, kurās pašvaldībai un tās kapitālsabiedrībām ir tieša ietekme: energopārvaldības sistēma pašvaldības ēkās, enerģijas patēriņa samazinājums ēkās un ielu apgaismojumā, AER īpatsvara pieaugums Rīgas pilsētas CSS un sabiedriskajā transportā. Savukārt mērķi, kuru izpilde atkarīga no iedzīvotāju un uzņēmumu lēmumiem, valsts atbalsta programmām vai nacionāla mēroga infrastruktūras, – daudzdzīvokļu ēku atjaunošana, AER izmantošana decentralizētajā siltumapgādē un elektroenerģijas ražošanā, transporta emisiju samazināšana – atpaliek no trajektorijas.
-Vairākiem mērķiem vidusposmā bija jāprecizē bāzes vērtības vai jāizmanto netieši rādītāji – piemēram, decentralizētās siltumapgādes un enerģijas ražošanas un transporta emisiju mērķiem bāzes vērtības noteiktas pēc SEG inventarizācijas datiem. Gatavojot SECAP2030 aktualizāciju, ieteicams pārskatīt mērķu formulējumus un bāzes vērtības un tos sasaistīt ar atjaunoto rādītāju sarakstu.
-Pārvaldības un monitoringa ziņā nepieciešamas vērienīgākās pārmaiņas. Vienota plāna ieviešanas koordinācija starp pašvaldības struktūrvienībām un kapitālsabiedrībām pagaidām nenotiek, un Klimata pilsētas līguma ieviešanai paredzētais sekretariāts netika izveidots. Tā kā REA kapacitāte ir ierobežota, daudzas iniciatīvas tiek īstenotas ES sadarbības projektos.
-Papildināt.</t>
+Labākie rezultāti sasniegti jomās, kurās pašvaldībai un tās kapitālsabiedrībām ir tieša ietekme: energopārvaldības sistēma pašvaldības ēkās, enerģijas patēriņa samazinājums ēkās un ielu apgaismojumā, AER īpatsvara pieaugums Rīgas pilsētas CSS un sabiedriskajā transportā. Savukārt mērķi, kuru izpilde atkarīga no iedzīvotāju un uzņēmumu lēmumiem, valsts atbalsta programmām vai nacionāla mēroga infrastruktūras, – daudzdzīvokļu ēku atjaunošana, AER izmantošana decentralizētajā siltumapgādē un elektroenerģijas ražošanā, transporta emisiju samazināšana – atpaliek no trajektorijas. AER īpatsvaram decentralizētajā siltumapgādē progresa nav – tas samazinājies no 41,8 % 2020. gadā līdz 34,2 % 2025. gadā, lai gan gada vērtības svārstās un dati nav viennozīmīgi (jāvienojas par aprēķina metodi).
+Vairākiem mērķiem vidusposmā bija jāprecizē bāzes vērtības vai jāizmanto netieši rādītāji. Gatavojot SECAP2030 aktualizāciju, ieteicams pārskatīt mērķu formulējumus un bāzes vērtības un tos sasaistīt ar atjaunoto rādītāju sarakstu.
+Pārvaldības un monitoringa ziņā nepieciešamas vērienīgākās pārmaiņas. Vienota plāna ieviešanas koordinācija starp pašvaldības struktūrvienībām un kapitālsabiedrībām pagaidām nenotiek, un Klimata pilsētas līguma ieviešanai paredzētais sekretariāts netika izveidots. Tā kā REA kapacitāte ir ierobežota, daudzas iniciatīvas tiek īstenotas ES sadarbības projektos.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>darba_versija</t>
+          <t>pasakumu_statusa_piezime</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Šī ir vidusposma pārskata darba versija. Saturs vēl tiek precizēts – aicinām pašvaldības kolēģus pārbaudīt informāciju un papildināt to, īpaši vietās, kas atzīmētas kā “Papildināt”.</t>
+          <t>Pasākumu statuss – REA vērtējums pēc pārskata teksta.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>aicinajums</t>
+          <t>en_summary</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Vai jums ir papildu informācija par kādu pasākumu vai rādītāju? Nospiediet “Papildināt” pie attiecīgā ieraksta – atvērsies e-pasta vēstule, kurā jau norādīts pasākuma vai rādītāja kods. Papildinājumi tiks iekļauti nākamajā pārskata versijā.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>pasakumu_statusa_piezime</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Pasākumu statuss ir darba versija – REA vērtējums pēc pārskata teksta, kas vēl tiks saskaņots ar atbildīgajām struktūrvienībām.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>en_summary</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
           <t>Riga's total CO₂ emissions in 2025 were 1,574 kt CO₂ – 9.6 % below 2019 (2030 target: −30 %) and 63.3 % below 1990 (target: −70 %). Progress towards the 2030 target stands at 32 %, so emission reductions are behind the linear trajectory.
-Of the 21 SECAP2030 targets assessed at mid-term, one has been achieved, seven are on track, nine are behind the trajectory and one shows no progress. Two targets (specific electricity use of traffic lights and the share of private car users) could not be assessed for lack of data. The heat-loss target is not assessed because network losses depend on weather conditions; the target needs to be revised.
-Municipal infrastructure. The energy management system is in place and certified (424 sites), energy use in municipal buildings has fallen by 13.7 %, and specific electricity use in street lighting has dropped to 0.392 MWh per luminaire – these targets are achieved or on track. Renewable energy in municipal heating, electricity and the vehicle fleet (12.0 % electric vehicles) is behind, and municipal emissions are down 27.3 % against a target of −100 %.
+Of the 21 SECAP2030 targets assessed at mid-term, three have been achieved, six are on track and eleven are behind the trajectory. One target (the share of private car users) could not be assessed for lack of comparable data. The heat-loss target was changed at mid-term in line with measure 3.1.3.11 of the National Energy and Climate Plan 2030: network losses during the active heating season are now assessed (&lt; 10 % by 2030).
+Municipal infrastructure. The energy management system is in place and certified (424 sites), energy use in municipal buildings has fallen by 13.7 %, specific electricity use in street lighting has dropped to 0.392 MWh per luminaire, and traffic-light bulbs have been replaced with LEDs – these targets are achieved or on track. Renewable energy in municipal heating, electricity and the vehicle fleet (12.0 % electric vehicles) is behind, and municipal emissions are down 27.3 % against a target of −100 %.
 Multi-apartment buildings. Climate-corrected heat use in buildings connected to district heating has fallen by 8.6 % and is on track. Only 209 of the targeted 2,000 buildings have been renovated, however; REA considers this target unattainable by 2030.
-Energy production. The renewable share in Riga's district heating has risen to 46.85 %, natural gas use has fallen by 27.3 % and the share of decentralised heating to 42.7 %. The renewable share in decentralised heating has declined (34.2 %), renewables provide only 6.7 % of the electricity generated in Riga, and emissions from energy production are 12.6 % below 2019 (target −30 %).
+Energy production. The renewable share in Riga's district heating has risen to 45.5 %, natural gas use has fallen by 27.3 % and the share of decentralised heating to 42.7 %. The renewable share in decentralised heating has declined (34.2 %), renewables provide only 6.7 % of the electricity generated in Riga, and emissions from energy production are 12.6 % below 2019 (target −30 %).
 Transport. The renewable share in public transport has reached 35.4 % and is on track, but transport emissions are only 6.2 % below 2019 and 26.3 % above 1990 (permitted: +21.5 %). Most transport emissions (720 of 758 kt CO₂) come from private transport.
-To reach the 2030 targets, implementation has to accelerate – above all in building renovation, renewable energy in decentralised heating and electricity generation, and cutting private-transport emissions. Coordination of plan implementation, financial planning and data management also need to be strengthened.</t>
+To reach the 2030 targets, implementation has to accelerate – above all in building renovation, renewable energy in decentralised heating and cutting private-transport emissions. Coordination of plan implementation, financial planning and data management also need to be strengthened.</t>
         </is>
       </c>
     </row>
@@ -6057,7 +5943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6484,18 +6370,6 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>VSIA</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>valsts sabiedrība ar ierobežotu atbildību</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
